--- a/DeepFace/Ergebnisse.xlsx
+++ b/DeepFace/Ergebnisse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eldarakhundzada/Desktop/8. Semester/BachelorThesis/DeepFace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146201B9-A58B-1A4C-9D34-3AB01A2B3958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEAEEFD-42EC-A74F-A5ED-79B1A81165EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4680" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{F8B601AC-B7A8-9541-AC5C-870221668981}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F8B601AC-B7A8-9541-AC5C-870221668981}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="239">
   <si>
     <t>Ethnie</t>
   </si>
@@ -755,6 +755,17 @@
   </si>
   <si>
     <t>0.2149</t>
+  </si>
+  <si>
+    <t>Direkter Vergleich:
+Also ob bei D oder S mehr True oder fals ist</t>
+  </si>
+  <si>
+    <t>Selber Hintergrund</t>
+  </si>
+  <si>
+    <t>Unterschiedlicher 
+Hintergrund</t>
   </si>
 </sst>
 </file>
@@ -966,9 +977,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -979,9 +987,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1006,6 +1011,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1058,17 +1069,17 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1165,62 +1176,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="brightRoom" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="flat">
-                <a:bevelT w="50800" h="101600" prst="angle"/>
-                <a:contourClr>
-                  <a:srgbClr val="000000"/>
-                </a:contourClr>
-              </a:sp3d>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-160E-9944-A7ED-28B9E9DD64BC}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-              <a:scene3d>
-                <a:camera prst="orthographicFront"/>
-                <a:lightRig rig="brightRoom" dir="t"/>
-              </a:scene3d>
-              <a:sp3d prstMaterial="flat">
-                <a:bevelT w="50800" h="101600" prst="angle"/>
-                <a:contourClr>
-                  <a:srgbClr val="000000"/>
-                </a:contourClr>
-              </a:sp3d>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-160E-9944-A7ED-28B9E9DD64BC}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -1277,31 +1232,11 @@
           <c:cat>
             <c:strRef>
               <c:f>Tabelle1!$A$130:$A$131</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Erfolgreiche Moprhs:</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Fehlgeschlagene 
-Morphs:</c:v>
-                </c:pt>
-              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Tabelle1!$B$130:$B$131</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>86</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>34</c:v>
-                </c:pt>
-              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -1469,187 +1404,14 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="20000"/>
-                  <a:lumOff val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-2D14-AA45-9C22-DFEED71AD618}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="20000"/>
-                  <a:lumOff val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-2D14-AA45-9C22-DFEED71AD618}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-2D14-AA45-9C22-DFEED71AD618}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000004-2D14-AA45-9C22-DFEED71AD618}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-2D14-AA45-9C22-DFEED71AD618}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="5"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000006-2D14-AA45-9C22-DFEED71AD618}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
           <c:cat>
             <c:strRef>
               <c:f>Tabelle1!$A$144:$A$149</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>Low mit Erfolg</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Low ohne Erfolg</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mid mit Erfolg</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Mid ohne Erfolg</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Hig mit Erfolg</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Hig ohne Erfolg</c:v>
-                </c:pt>
-              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Tabelle1!$B$144:$B$149</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>34</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>26</c:v>
-                </c:pt>
-              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -3594,6 +3356,266 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-DD27-0948-AEB2-3B2CCDCF4E82}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$G$170:$G$171</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Selber Hintergrund</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Unterschiedlicher 
+Hintergrund</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$H$170:$H$171</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DD27-0948-AEB2-3B2CCDCF4E82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="105947392"/>
+        <c:axId val="106405680"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="105947392"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="106405680"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="106405680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="105947392"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3874,6 +3896,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="258">
   <cs:axisTitle>
@@ -6907,6 +6969,509 @@
 </file>
 
 <file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7663,6 +8228,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>152977</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>162983</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>837046</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>183380</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Diagramm 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88D0ACFF-8E20-68CD-C3C3-5F8AD77B11E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7722,32 +8323,32 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9D87EE29-B3D0-7740-90E8-3E1D9E7C8D17}" name="Tabelle10" displayName="Tabelle10" ref="A223:B226" totalsRowShown="0" headerRowDxfId="15" dataDxfId="12" tableBorderDxfId="16" dataCellStyle="Standard">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{9D87EE29-B3D0-7740-90E8-3E1D9E7C8D17}" name="Tabelle10" displayName="Tabelle10" ref="A223:B226" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14" dataCellStyle="Standard">
   <autoFilter ref="A223:B226" xr:uid="{9D87EE29-B3D0-7740-90E8-3E1D9E7C8D17}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8FF92EEC-9432-C641-B7FE-1BB696D1CD83}" name="Spalte1" dataDxfId="14" dataCellStyle="Standard"/>
-    <tableColumn id="2" xr3:uid="{ECE6D1EA-1AD6-6240-A14D-BA36B7A511BE}" name="Spalte2" dataDxfId="13" dataCellStyle="Standard"/>
+    <tableColumn id="1" xr3:uid="{8FF92EEC-9432-C641-B7FE-1BB696D1CD83}" name="Spalte1" dataDxfId="13" dataCellStyle="Standard"/>
+    <tableColumn id="2" xr3:uid="{ECE6D1EA-1AD6-6240-A14D-BA36B7A511BE}" name="Spalte2" dataDxfId="12" dataCellStyle="Standard"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{88697EEA-2683-794E-8030-BD24ECD65B08}" name="Tabelle11" displayName="Tabelle11" ref="A231:B234" totalsRowShown="0" headerRowDxfId="8" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{88697EEA-2683-794E-8030-BD24ECD65B08}" name="Tabelle11" displayName="Tabelle11" ref="A231:B234" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A231:B234" xr:uid="{88697EEA-2683-794E-8030-BD24ECD65B08}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{B19A7482-D677-5E45-912F-3366E0E17A53}" name="Spalte1" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{335E9F4F-30A2-834E-9173-834131AFA280}" name="Spalte2" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{B19A7482-D677-5E45-912F-3366E0E17A53}" name="Spalte1" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{335E9F4F-30A2-834E-9173-834131AFA280}" name="Spalte2" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{918BE932-4829-E848-8BFA-F9C2CDB059BC}" name="Tabelle12" displayName="Tabelle12" ref="A242:B244" totalsRowShown="0" headerRowDxfId="5" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{918BE932-4829-E848-8BFA-F9C2CDB059BC}" name="Tabelle12" displayName="Tabelle12" ref="A242:B244" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A242:B244" xr:uid="{918BE932-4829-E848-8BFA-F9C2CDB059BC}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{32933E8B-3554-794A-AC32-FB92ADA5C69F}" name="Spalte1" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{32933E8B-3554-794A-AC32-FB92ADA5C69F}" name="Spalte1" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{781A3187-0998-0D43-A1E3-E3DD786D6502}" name="Spalte2" dataDxfId="4">
       <calculatedColumnFormula>COUNTIFS(C1:C120, "Woman", H1:H120, "True", I1:I120, "D")</calculatedColumnFormula>
     </tableColumn>
@@ -7757,11 +8358,11 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5CBE8236-0976-8F41-8E83-42626148532D}" name="Tabelle13" displayName="Tabelle13" ref="A263:B265" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5CBE8236-0976-8F41-8E83-42626148532D}" name="Tabelle13" displayName="Tabelle13" ref="A263:B265" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <autoFilter ref="A263:B265" xr:uid="{5CBE8236-0976-8F41-8E83-42626148532D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DA27F37D-ECC4-9247-B520-4773B2097D48}" name="Spalte1" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{CA3B673D-2F9E-B84B-9875-CD2D9D1C2E37}" name="Spalte2" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{DA27F37D-ECC4-9247-B520-4773B2097D48}" name="Spalte1" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{CA3B673D-2F9E-B84B-9875-CD2D9D1C2E37}" name="Spalte2" dataDxfId="0">
       <calculatedColumnFormula>COUNTIFS(D1:D120, "30-40", H1:H120, "True", I1:I120, "D")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8086,6 +8687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E937269-5730-0745-BDE6-3F3B154E2F73}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J265"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -8125,236 +8727,236 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3">
-        <v>101</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>16</v>
+      <c r="F2" s="4">
+        <v>260</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="I2" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J2" s="4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3">
-        <v>105</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>17</v>
+      <c r="F3" s="5">
+        <v>454</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J3" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3">
-        <v>101</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>18</v>
+      <c r="J3" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="6">
+        <v>37</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J4" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="I4" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J4" s="6">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="3">
-        <v>578</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>19</v>
+      <c r="F5" s="6">
+        <v>759</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="J5" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="J5" s="6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="6">
+        <v>330</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J6" s="6">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="12">
+        <v>273</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="J7" s="12">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="3">
-        <v>101</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J6" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="11">
-        <v>560</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="J7" s="11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="4">
-        <v>779</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>27</v>
+      <c r="F8" s="5">
+        <v>658</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J8" s="4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I8" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J8" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>9</v>
+        <v>118</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>10</v>
@@ -8366,10 +8968,10 @@
         <v>12</v>
       </c>
       <c r="F9" s="4">
-        <v>273</v>
+        <v>129</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>15</v>
@@ -8378,47 +8980,47 @@
         <v>211</v>
       </c>
       <c r="J9" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="4">
-        <v>779</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>29</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="5">
+        <v>114</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J10" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I10" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J10" s="5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>10</v>
@@ -8427,13 +9029,13 @@
         <v>26</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" s="4">
-        <v>56</v>
+        <v>603</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>30</v>
+        <v>165</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>15</v>
@@ -8442,111 +9044,111 @@
         <v>211</v>
       </c>
       <c r="J11" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="4">
-        <v>779</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>31</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="6">
+        <v>3</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J12" s="4">
+      <c r="I12" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J12" s="6">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="12" t="s">
+      <c r="E13" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="11">
+        <v>161</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="J13" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="12">
-        <v>241</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="J13" s="12">
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="5">
-        <v>7</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>37</v>
+      <c r="F14" s="3">
+        <v>105</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J14" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I14" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>36</v>
@@ -8555,13 +9157,13 @@
         <v>11</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F15" s="5">
-        <v>658</v>
+        <v>168</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>15</v>
@@ -8570,175 +9172,175 @@
         <v>211</v>
       </c>
       <c r="J15" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="5">
-        <v>7</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>39</v>
+      <c r="F16" s="4">
+        <v>778</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J16" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="I16" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J16" s="4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="5">
-        <v>746</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>40</v>
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3">
+        <v>604</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="J17" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="5" t="s">
+      <c r="J17" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="6">
+        <v>639</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J18" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="7">
+        <v>114</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="J19" s="7">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="5">
-        <v>7</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J18" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="13">
-        <v>25</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="J19" s="13">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="6">
-        <v>916</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>43</v>
+      <c r="E20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="3">
+        <v>264</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="J20" s="6">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I20" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J20" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>36</v>
@@ -8747,13 +9349,13 @@
         <v>26</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F21" s="6">
-        <v>639</v>
+        <v>312</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>15</v>
@@ -8762,143 +9364,143 @@
         <v>211</v>
       </c>
       <c r="J21" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="6">
-        <v>916</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>48</v>
+      <c r="F22" s="3">
+        <v>879</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="J22" s="6">
-        <v>21</v>
+      <c r="I22" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J22" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="A23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="6">
-        <v>342</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>49</v>
+      <c r="C23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3">
+        <v>101</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="5">
+        <v>119</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J23" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="6">
-        <v>916</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="J24" s="6">
-        <v>23</v>
+      <c r="J24" s="5">
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="7">
-        <v>400</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>51</v>
+      <c r="A25" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="11">
+        <v>164</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="H25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="J25" s="7">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I25" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="J25" s="11">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>10</v>
@@ -8907,62 +9509,62 @@
         <v>11</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26" s="3">
-        <v>253</v>
+        <v>578</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J26" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="3">
-        <v>604</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>57</v>
+      <c r="F27" s="5">
+        <v>240</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J27" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J27" s="5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>10</v>
@@ -8974,187 +9576,187 @@
         <v>13</v>
       </c>
       <c r="F28" s="3">
-        <v>253</v>
+        <v>361</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J28" s="3">
-        <v>27</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="A29" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="3">
-        <v>264</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>59</v>
+      <c r="E29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="6">
+        <v>777</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J29" s="3">
-        <v>28</v>
+      <c r="I29" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="J29" s="6">
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="A30" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="5">
+        <v>17</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J30" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" s="3">
-        <v>253</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J30" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" s="11">
-        <v>482</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>61</v>
+      <c r="D31" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="12">
+        <v>779</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I31" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="J31" s="11">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="4" t="s">
+      <c r="I31" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="J31" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="D32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="4">
-        <v>471</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>196</v>
+      <c r="F32" s="3">
+        <v>81</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J32" s="4">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="4">
-        <v>260</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>194</v>
+      <c r="I32" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J32" s="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="5">
+        <v>362</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="4">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J33" s="5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>192</v>
+        <v>90</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>10</v>
@@ -9163,30 +9765,30 @@
         <v>26</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F34" s="4">
-        <v>471</v>
+        <v>181</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J34" s="4">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>10</v>
@@ -9198,10 +9800,10 @@
         <v>13</v>
       </c>
       <c r="F35" s="4">
-        <v>579</v>
+        <v>398</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>15</v>
@@ -9210,175 +9812,175 @@
         <v>211</v>
       </c>
       <c r="J35" s="4">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B36" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="6">
+        <v>342</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J36" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="13">
+        <v>746</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="J37" s="13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" s="4">
-        <v>471</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J36" s="4">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" s="12">
-        <v>300</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="J37" s="12">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="5">
-        <v>17</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>65</v>
+      <c r="F38" s="3">
+        <v>253</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I38" s="5" t="s">
+      <c r="I38" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J38" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B39" s="5" t="s">
+      <c r="J38" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="5">
-        <v>454</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>66</v>
+      <c r="D39" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" s="6">
+        <v>684</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I39" s="5" t="s">
+      <c r="I39" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="J39" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="5" t="s">
+      <c r="J39" s="6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D40" s="5" t="s">
+      <c r="C40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="5">
-        <v>17</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>67</v>
+      <c r="E40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" s="3">
+        <v>482</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J40" s="5">
-        <v>39</v>
+      <c r="I40" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J40" s="3">
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>36</v>
@@ -9387,86 +9989,86 @@
         <v>11</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F41" s="5">
-        <v>440</v>
+        <v>104</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J41" s="5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="4">
+        <v>779</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J42" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="12">
+        <v>223</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="J41" s="5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" s="5">
-        <v>17</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J42" s="5">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" s="13">
-        <v>672</v>
-      </c>
-      <c r="G43" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H43" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="J43" s="13">
-        <v>42</v>
+      <c r="J43" s="12">
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -9501,12 +10103,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>71</v>
+        <v>181</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>36</v>
@@ -9515,13 +10117,13 @@
         <v>26</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F45" s="6">
-        <v>37</v>
+        <v>729</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="H45" s="8" t="s">
         <v>15</v>
@@ -9530,15 +10132,15 @@
         <v>211</v>
       </c>
       <c r="J45" s="6">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>36</v>
@@ -9547,13 +10149,13 @@
         <v>26</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F46" s="6">
-        <v>322</v>
+        <v>212</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="H46" s="8" t="s">
         <v>15</v>
@@ -9562,268 +10164,268 @@
         <v>212</v>
       </c>
       <c r="J46" s="6">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C47" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="6">
-        <v>312</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>77</v>
+      <c r="F47" s="5">
+        <v>824</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="I47" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J47" s="6">
-        <v>46</v>
+      <c r="J47" s="5">
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D48" s="6" t="s">
+      <c r="A48" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F48" s="6">
-        <v>322</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I48" s="6" t="s">
+      <c r="E48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="4">
+        <v>182</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J48" s="6">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A49" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49" s="7">
-        <v>684</v>
-      </c>
-      <c r="G49" s="7" t="s">
+      <c r="J48" s="4">
         <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="11">
+        <v>173</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>87</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I49" s="7" t="s">
+      <c r="I49" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="J49" s="7">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="3" t="s">
+      <c r="J49" s="11">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="3">
-        <v>164</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>84</v>
+      <c r="E50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="6">
+        <v>274</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I50" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J50" s="3">
-        <v>49</v>
+      <c r="I50" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J50" s="6">
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="3" t="s">
+      <c r="A51" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F51" s="3">
-        <v>161</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>85</v>
+      <c r="F51" s="5">
+        <v>7</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I51" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J51" s="3">
-        <v>50</v>
+      <c r="I51" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J51" s="5">
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="3">
-        <v>164</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>86</v>
+      <c r="A52" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="6">
+        <v>371</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>182</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="I52" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J52" s="3">
-        <v>51</v>
+      <c r="J52" s="6">
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="A53" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="3" t="s">
+      <c r="D53" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="3">
-        <v>173</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>87</v>
+      <c r="F53" s="4">
+        <v>471</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>197</v>
       </c>
       <c r="H53" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I53" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J53" s="3">
-        <v>52</v>
+      <c r="I53" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J53" s="4">
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A54" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" s="3" t="s">
+      <c r="A54" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="3">
-        <v>164</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>88</v>
+      <c r="D54" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="4">
+        <v>190</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="H54" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="I54" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J54" s="3">
-        <v>53</v>
+      <c r="J54" s="4">
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>83</v>
@@ -9835,190 +10437,190 @@
         <v>11</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F55" s="11">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="H55" s="14" t="s">
-        <v>20</v>
+        <v>86</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J55" s="11">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="4">
-        <v>190</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>199</v>
+      <c r="A56" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="6">
+        <v>777</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="H56" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I56" s="4" t="s">
+      <c r="I56" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J56" s="4">
-        <v>55</v>
+      <c r="J56" s="6">
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="4" t="s">
+      <c r="A57" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F57" s="4">
-        <v>181</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>200</v>
+      <c r="F57" s="5">
+        <v>31</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="H57" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I57" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J57" s="4">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C58" s="4" t="s">
+      <c r="I57" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J57" s="5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="4">
-        <v>190</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>93</v>
+      <c r="D58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="3">
+        <v>281</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="H58" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J58" s="4">
-        <v>57</v>
+      <c r="I58" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J58" s="3">
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C59" s="4" t="s">
+      <c r="A59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E59" s="4" t="s">
+      <c r="D59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F59" s="4">
-        <v>223</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>94</v>
+      <c r="F59" s="3">
+        <v>253</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="H59" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I59" s="4" t="s">
+      <c r="I59" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J59" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" s="5">
+        <v>717</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J59" s="4">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F60" s="4">
-        <v>190</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J60" s="4">
-        <v>59</v>
+      <c r="J60" s="5">
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
-        <v>92</v>
+        <v>191</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>10</v>
@@ -10027,126 +10629,126 @@
         <v>26</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F61" s="12">
-        <v>138</v>
+        <v>471</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>20</v>
+        <v>196</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J61" s="12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="5">
-        <v>104</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>100</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="4">
+        <v>579</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>235</v>
       </c>
       <c r="H62" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I62" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J62" s="5">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A63" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F63" s="5">
-        <v>114</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>101</v>
+      <c r="I62" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J62" s="4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" s="4">
+        <v>239</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="H63" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I63" s="5" t="s">
+      <c r="I63" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="J63" s="5">
-        <v>62</v>
+      <c r="J63" s="4">
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A64" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="5">
-        <v>104</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H64" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I64" s="5" t="s">
+      <c r="A64" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="4">
+        <v>515</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J64" s="5">
-        <v>63</v>
+      <c r="J64" s="4">
+        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>36</v>
@@ -10158,27 +10760,27 @@
         <v>13</v>
       </c>
       <c r="F65" s="5">
-        <v>168</v>
+        <v>7</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="H65" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J65" s="5">
-        <v>64</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>36</v>
@@ -10187,62 +10789,62 @@
         <v>11</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F66" s="5">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>20</v>
+        <v>67</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>212</v>
       </c>
       <c r="J66" s="5">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A67" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F67" s="13">
-        <v>717</v>
-      </c>
-      <c r="G67" s="13" t="s">
-        <v>105</v>
+      <c r="A67" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="12">
+        <v>182</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I67" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="J67" s="13">
-        <v>66</v>
+      <c r="I67" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="J67" s="12">
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>36</v>
@@ -10254,10 +10856,10 @@
         <v>12</v>
       </c>
       <c r="F68" s="6">
-        <v>212</v>
+        <v>916</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="H68" s="8" t="s">
         <v>15</v>
@@ -10266,556 +10868,556 @@
         <v>212</v>
       </c>
       <c r="J68" s="6">
-        <v>67</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E69" s="6" t="s">
+      <c r="A69" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F69" s="6">
-        <v>114</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>110</v>
+      <c r="F69" s="3">
+        <v>174</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H69" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I69" s="6" t="s">
+      <c r="I69" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J69" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" s="4">
+        <v>186</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="J69" s="6">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A70" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C70" s="6" t="s">
+      <c r="J70" s="4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="6">
-        <v>212</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="J70" s="6">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A71" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="6">
-        <v>146</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I71" s="6" t="s">
+      <c r="D71" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" s="5">
+        <v>793</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J71" s="6">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J71" s="5">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F72" s="6">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>20</v>
+        <v>150</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J72" s="6">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A73" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="7">
-        <v>183</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>114</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="11">
+        <v>802</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>156</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I73" s="7" t="s">
+      <c r="I73" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="J73" s="7">
+      <c r="J73" s="11">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A74" s="6" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A74" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" s="3">
-        <v>174</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>119</v>
+      <c r="B74" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="6">
+        <v>322</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="H74" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I74" s="3" t="s">
+      <c r="I74" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J74" s="3">
-        <v>73</v>
+      <c r="J74" s="6">
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C75" s="3" t="s">
+      <c r="A75" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="3">
-        <v>81</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>120</v>
+      <c r="D75" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="4">
+        <v>190</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="H75" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I75" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J75" s="3">
-        <v>74</v>
+      <c r="I75" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J75" s="4">
+        <v>57</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="3" t="s">
+      <c r="A76" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F76" s="3">
-        <v>174</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>121</v>
+      <c r="F76" s="6">
+        <v>916</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="H76" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I76" s="3" t="s">
+      <c r="I76" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J76" s="3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C77" s="3" t="s">
+      <c r="J76" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E77" s="3" t="s">
+      <c r="D77" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F77" s="3">
-        <v>361</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>122</v>
+      <c r="F77" s="4">
+        <v>56</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="H77" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I77" s="3" t="s">
+      <c r="I77" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="J77" s="3">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C78" s="3" t="s">
+      <c r="J77" s="4">
         <v>10</v>
       </c>
-      <c r="D78" s="3" t="s">
+    </row>
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" s="6">
+        <v>400</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J78" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A79" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" s="12">
+        <v>779</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="J79" s="12">
         <v>11</v>
       </c>
-      <c r="E78" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F78" s="3">
-        <v>174</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J78" s="3">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A79" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C79" s="11" t="s">
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A80" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="D80" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E79" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F79" s="11">
-        <v>650</v>
-      </c>
-      <c r="G79" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="H79" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I79" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="J79" s="11">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A80" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F80" s="4">
-        <v>182</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>128</v>
+      <c r="E80" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="3">
+        <v>101</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="H80" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I80" s="4" t="s">
+      <c r="I80" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J80" s="4">
-        <v>79</v>
+      <c r="J80" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A81" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B81" s="4" t="s">
+      <c r="A81" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F81" s="4">
-        <v>129</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>129</v>
+      <c r="D81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="3">
+        <v>174</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="H81" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I81" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J81" s="4">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A82" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D82" s="4" t="s">
+      <c r="I81" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J81" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D82" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E82" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="4">
-        <v>182</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>130</v>
+      <c r="E82" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" s="6">
+        <v>183</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="H82" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I82" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J82" s="4">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A83" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="4">
-        <v>398</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>131</v>
+      <c r="I82" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J82" s="6">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="5">
+        <v>374</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>174</v>
       </c>
       <c r="H83" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I83" s="4" t="s">
+      <c r="I83" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J83" s="4">
+      <c r="J83" s="5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A84" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="5">
+        <v>369</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J84" s="5">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A85" s="11" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A84" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C84" s="4" t="s">
+      <c r="B85" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C85" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E84" s="4" t="s">
+      <c r="D85" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F84" s="4">
-        <v>182</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I84" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J84" s="4">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A85" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E85" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F85" s="12">
-        <v>186</v>
-      </c>
-      <c r="G85" s="12" t="s">
-        <v>132</v>
+      <c r="F85" s="11">
+        <v>164</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I85" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="J85" s="12">
-        <v>84</v>
+      <c r="I85" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="J85" s="11">
+        <v>53</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>118</v>
@@ -10827,13 +11429,13 @@
         <v>26</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F86" s="5">
         <v>31</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>15</v>
@@ -10842,30 +11444,30 @@
         <v>212</v>
       </c>
       <c r="J86" s="5">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F87" s="5">
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="H87" s="8" t="s">
         <v>15</v>
@@ -10874,204 +11476,204 @@
         <v>211</v>
       </c>
       <c r="J87" s="5">
-        <v>86</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A88" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C88" s="5" t="s">
+      <c r="A88" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C88" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D88" s="5" t="s">
+      <c r="D88" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="E88" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F88" s="5">
-        <v>31</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="H88" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I88" s="5" t="s">
+      <c r="F88" s="6">
+        <v>371</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I88" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J88" s="5">
-        <v>87</v>
+      <c r="J88" s="6">
+        <v>117</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F89" s="5">
-        <v>824</v>
+        <v>7</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="H89" s="8" t="s">
-        <v>15</v>
+        <v>41</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J89" s="5">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A90" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B90" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C90" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E90" s="5" t="s">
+      <c r="C90" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F90" s="5">
-        <v>31</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>140</v>
+      <c r="F90" s="3">
+        <v>650</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="H90" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I90" s="5" t="s">
+      <c r="I90" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J90" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A91" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91" s="11">
+        <v>101</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H91" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="J90" s="5">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A91" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B91" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C91" s="13" t="s">
+      <c r="J91" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A92" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F92" s="4">
+        <v>190</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J92" s="4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93" s="4">
+        <v>300</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J93" s="4">
         <v>36</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F91" s="13">
-        <v>119</v>
-      </c>
-      <c r="G91" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I91" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="J91" s="13">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A92" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F92" s="6">
-        <v>777</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="H92" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="J92" s="6">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A93" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F93" s="6">
-        <v>3</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H93" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J93" s="6">
-        <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>118</v>
@@ -11083,123 +11685,123 @@
         <v>11</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F94" s="6">
         <v>777</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="H94" s="8" t="s">
-        <v>15</v>
+        <v>149</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="I94" s="6" t="s">
         <v>212</v>
       </c>
       <c r="J94" s="6">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A95" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B95" s="6" t="s">
+      <c r="A95" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" s="4">
+        <v>515</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J95" s="4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C95" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D95" s="6" t="s">
+      <c r="C96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E95" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="6">
-        <v>274</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="H95" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J95" s="6">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A96" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="6" t="s">
+      <c r="E96" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F96" s="6">
-        <v>777</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>149</v>
+      <c r="F96" s="3">
+        <v>174</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="H96" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I96" s="6" t="s">
+      <c r="I96" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J96" s="6">
-        <v>95</v>
+      <c r="J96" s="3">
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A97" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C97" s="7" t="s">
+      <c r="A97" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C97" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="D97" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E97" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F97" s="7">
-        <v>83</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I97" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="J97" s="7">
-        <v>96</v>
+      <c r="E97" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="13">
+        <v>104</v>
+      </c>
+      <c r="G97" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H97" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="J97" s="13">
+        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>154</v>
@@ -11211,13 +11813,13 @@
         <v>11</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F98" s="3">
         <v>813</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H98" s="9" t="s">
         <v>20</v>
@@ -11226,47 +11828,47 @@
         <v>212</v>
       </c>
       <c r="J98" s="3">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A99" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C99" s="3" t="s">
+      <c r="A99" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F99" s="3">
-        <v>802</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H99" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J99" s="3">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D99" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F99" s="4">
+        <v>471</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J99" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>10</v>
@@ -11275,278 +11877,278 @@
         <v>11</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F100" s="3">
-        <v>813</v>
+        <v>177</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="H100" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J100" s="3">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A101" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D101" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D101" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F101" s="3">
-        <v>879</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="H101" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I101" s="3" t="s">
+      <c r="E101" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F101" s="5">
+        <v>672</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I101" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J101" s="3">
-        <v>100</v>
+      <c r="J101" s="5">
+        <v>42</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A102" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D102" s="3" t="s">
+      <c r="A102" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D102" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E102" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F102" s="3">
-        <v>813</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>159</v>
+      <c r="F102" s="5">
+        <v>17</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="H102" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I102" s="3" t="s">
+      <c r="I102" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J102" s="3">
-        <v>101</v>
+      <c r="J102" s="5">
+        <v>41</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A103" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="B103" s="11" t="s">
+      <c r="A103" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103" s="12">
+        <v>182</v>
+      </c>
+      <c r="G103" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="H103" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I103" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="J103" s="12">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A104" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C104" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D103" s="11" t="s">
+      <c r="D104" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E103" s="11" t="s">
+      <c r="E104" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F104" s="3">
+        <v>813</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J104" s="3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A105" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E105" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F103" s="11">
-        <v>281</v>
-      </c>
-      <c r="G103" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I103" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="J103" s="11">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A104" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C104" s="4" t="s">
+      <c r="F105" s="6">
+        <v>916</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="J105" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F104" s="4">
-        <v>515</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H104" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I104" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J104" s="4">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A105" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F105" s="4">
-        <v>603</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="H105" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I105" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J105" s="4">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A106" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F106" s="4">
-        <v>515</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>166</v>
+      <c r="D106" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106" s="3">
+        <v>560</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I106" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J106" s="4">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A107" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B107" s="4" t="s">
+      <c r="I106" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J106" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F107" s="5">
+        <v>25</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I107" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J107" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A108" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B108" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C107" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F107" s="4">
-        <v>778</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="H107" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I107" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J107" s="4">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A108" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E108" s="4" t="s">
+      <c r="C108" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F108" s="4">
-        <v>515</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>168</v>
+      <c r="F108" s="5">
+        <v>369</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>177</v>
       </c>
       <c r="H108" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I108" s="4" t="s">
+      <c r="I108" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J108" s="4">
-        <v>107</v>
+      <c r="J108" s="5">
+        <v>113</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.2">
@@ -11566,19 +12168,19 @@
         <v>14</v>
       </c>
       <c r="F109" s="12">
-        <v>239</v>
+        <v>515</v>
       </c>
       <c r="G109" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>15</v>
+        <v>168</v>
+      </c>
+      <c r="H109" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="I109" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J109" s="12">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
@@ -11614,232 +12216,232 @@
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A111" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B111" s="5" t="s">
+      <c r="A111" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C111" s="5" t="s">
+      <c r="C111" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F111" s="3">
+        <v>813</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J111" s="3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F112" s="4">
+        <v>138</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J112" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F113" s="4">
+        <v>241</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J113" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A114" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C114" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D111" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F111" s="5">
-        <v>374</v>
-      </c>
-      <c r="G111" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="H111" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I111" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J111" s="5">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A112" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="5">
-        <v>369</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="H112" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I112" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J112" s="5">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A113" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F113" s="5">
-        <v>362</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="H113" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I113" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J113" s="5">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A114" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="5" t="s">
+      <c r="D114" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E114" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F114" s="5">
-        <v>369</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>177</v>
+      <c r="F114" s="6">
+        <v>322</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="H114" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I114" s="5" t="s">
+      <c r="I114" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J114" s="5">
+      <c r="J114" s="6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A115" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F115" s="7">
+        <v>212</v>
+      </c>
+      <c r="G115" s="7" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A115" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="B115" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="C115" s="13" t="s">
+      <c r="H115" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="J115" s="7">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A116" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F116" s="3">
+        <v>253</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J116" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A117" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D115" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E115" s="13" t="s">
+      <c r="D117" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E117" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F115" s="13">
-        <v>793</v>
-      </c>
-      <c r="G115" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I115" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="J115" s="13">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A116" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F116" s="6">
-        <v>371</v>
-      </c>
-      <c r="G116" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H116" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I116" s="6" t="s">
+      <c r="F117" s="5">
+        <v>31</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I117" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J116" s="6">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A117" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F117" s="6">
-        <v>330</v>
-      </c>
-      <c r="G117" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H117" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I117" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J117" s="6">
-        <v>116</v>
+      <c r="J117" s="5">
+        <v>89</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>154</v>
@@ -11851,13 +12453,13 @@
         <v>26</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F118" s="6">
         <v>371</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H118" s="9" t="s">
         <v>20</v>
@@ -11866,47 +12468,47 @@
         <v>212</v>
       </c>
       <c r="J118" s="6">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A119" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C119" s="6" t="s">
+      <c r="A119" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D119" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E119" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F119" s="6">
-        <v>759</v>
-      </c>
-      <c r="G119" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="H119" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I119" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J119" s="6">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D119" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F119" s="5">
+        <v>104</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I119" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J119" s="5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>36</v>
@@ -11915,30 +12517,30 @@
         <v>26</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F120" s="6">
-        <v>371</v>
+        <v>146</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="H120" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J120" s="6">
-        <v>119</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="7" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>36</v>
@@ -11947,44 +12549,48 @@
         <v>26</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F121" s="7">
-        <v>729</v>
+        <v>212</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>15</v>
+        <v>111</v>
+      </c>
+      <c r="H121" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J121" s="7">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A125" s="20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="B125" s="20"/>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A126" s="20"/>
-      <c r="B126" s="20"/>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A128" s="18" t="s">
+      <c r="B125" s="27"/>
+    </row>
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="27"/>
+      <c r="B126" s="27"/>
+    </row>
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="17" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A129" s="17"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A130" s="17" t="s">
+    <row r="129" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="16"/>
+    </row>
+    <row r="130" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="16" t="s">
         <v>203</v>
       </c>
       <c r="B130" s="1">
@@ -11992,8 +12598,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A131" s="16" t="s">
+    <row r="131" spans="1:2" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="15" t="s">
         <v>204</v>
       </c>
       <c r="B131" s="1">
@@ -12001,12 +12607,23 @@
         <v>34</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A140" s="19" t="s">
+    <row r="132" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="133" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="134" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="135" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="136" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="137" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="138" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="139" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="140" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="18" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="142" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="143" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="144" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>207</v>
       </c>
@@ -12015,7 +12632,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
         <v>206</v>
       </c>
@@ -12024,7 +12641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>208</v>
       </c>
@@ -12033,7 +12650,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>209</v>
       </c>
@@ -12042,7 +12659,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>215</v>
       </c>
@@ -12051,7 +12668,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>216</v>
       </c>
@@ -12060,30 +12677,37 @@
         <v>26</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A156" s="22" t="s">
+    <row r="150" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="151" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="152" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="153" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="154" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="155" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="156" spans="1:2" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="20" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A158" s="24" t="s">
+    <row r="157" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="158" spans="1:2" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="B158" s="23">
+      <c r="B158" s="21">
         <f>COUNTIFS( I2:I121, "D")</f>
         <v>60</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A160" s="21" t="s">
+      <c r="A160" s="19" t="s">
         <v>222</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A161" s="21" t="s">
+    <row r="161" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A161" s="19" t="s">
         <v>217</v>
       </c>
       <c r="B161" s="1">
@@ -12091,8 +12715,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A162" s="21" t="s">
+    <row r="162" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A162" s="19" t="s">
         <v>218</v>
       </c>
       <c r="B162" s="1">
@@ -12100,8 +12724,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A163" s="21" t="s">
+    <row r="163" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A163" s="19" t="s">
         <v>219</v>
       </c>
       <c r="B163" s="1">
@@ -12109,23 +12733,46 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A164" s="21"/>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A165" s="21"/>
-    </row>
-    <row r="174" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A174" s="24" t="s">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A164" s="19"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A165" s="19"/>
+    </row>
+    <row r="169" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+      <c r="G169" s="19" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G170" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H170" s="1">
+        <f>COUNTIFS(I2:I121, "S", H2:H121, "True")</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="G171" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="H171" s="1">
+        <f>COUNTIFS(I2:I121, "D", H2:H121, "True")</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A174" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="B174" s="23">
+      <c r="B174" s="21">
         <f>COUNTIFS( I2:I121, "S")</f>
         <v>60</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A176" s="21" t="s">
+    <row r="176" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+      <c r="A176" s="19" t="s">
         <v>222</v>
       </c>
       <c r="B176" s="1" t="s">
@@ -12133,7 +12780,7 @@
       </c>
     </row>
     <row r="177" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A177" s="21" t="s">
+      <c r="A177" s="19" t="s">
         <v>217</v>
       </c>
       <c r="B177" s="1">
@@ -12142,7 +12789,7 @@
       </c>
     </row>
     <row r="178" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A178" s="21" t="s">
+      <c r="A178" s="19" t="s">
         <v>218</v>
       </c>
       <c r="B178" s="1">
@@ -12151,7 +12798,7 @@
       </c>
     </row>
     <row r="179" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A179" s="21" t="s">
+      <c r="A179" s="19" t="s">
         <v>219</v>
       </c>
       <c r="B179" s="1">
@@ -12160,27 +12807,27 @@
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A180" s="21"/>
+      <c r="A180" s="19"/>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A181" s="21"/>
+      <c r="A181" s="19"/>
     </row>
     <row r="191" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A191" s="22" t="s">
+      <c r="A191" s="20" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A194" s="23" t="s">
+      <c r="A194" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="B194" s="23">
+      <c r="B194" s="21">
         <f>COUNTIFS( B2:B121, "Asian", I2:I121, "D")</f>
         <v>12</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A197" s="21" t="s">
+      <c r="A197" s="19" t="s">
         <v>222</v>
       </c>
       <c r="B197" s="1" t="s">
@@ -12188,7 +12835,7 @@
       </c>
     </row>
     <row r="198" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A198" s="21" t="s">
+      <c r="A198" s="19" t="s">
         <v>217</v>
       </c>
       <c r="B198" s="1">
@@ -12197,7 +12844,7 @@
       </c>
     </row>
     <row r="199" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A199" s="21" t="s">
+      <c r="A199" s="19" t="s">
         <v>218</v>
       </c>
       <c r="B199" s="1">
@@ -12206,7 +12853,7 @@
       </c>
     </row>
     <row r="200" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A200" s="21" t="s">
+      <c r="A200" s="19" t="s">
         <v>219</v>
       </c>
       <c r="B200" s="1">
@@ -12215,16 +12862,16 @@
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A203" s="23" t="s">
+      <c r="A203" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="B203" s="23">
+      <c r="B203" s="21">
         <f>COUNTIFS( B2:B121, "Black", I2:I121, "D")</f>
         <v>12</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A206" s="21" t="s">
+      <c r="A206" s="19" t="s">
         <v>222</v>
       </c>
       <c r="B206" s="1" t="s">
@@ -12232,184 +12879,184 @@
       </c>
     </row>
     <row r="207" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A207" s="21" t="s">
+      <c r="A207" s="19" t="s">
         <v>217</v>
       </c>
       <c r="B207" s="1">
         <f>COUNTIFS( B2:B121, "Black", I2:I121, "D", H2:H121, "True", E2:E121, "Low")</f>
         <v>4</v>
       </c>
-      <c r="D207" s="23" t="s">
+      <c r="D207" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="E207" s="23"/>
+      <c r="E207" s="21"/>
     </row>
     <row r="208" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A208" s="21" t="s">
+      <c r="A208" s="19" t="s">
         <v>218</v>
       </c>
       <c r="B208" s="1">
         <f>COUNTIFS( B2:B121, "Black", I2:I121, "D", H2:H121, "True", E2:E121, "Mid")</f>
         <v>4</v>
       </c>
-      <c r="D208" s="23" t="s">
+      <c r="D208" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="E208" s="23">
+      <c r="E208" s="21">
         <v>4</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A209" s="21" t="s">
+      <c r="A209" s="19" t="s">
         <v>219</v>
       </c>
       <c r="B209" s="1">
         <f>COUNTIFS( B2:B121, "Black", I2:I121, "D", H2:H121, "True", E2:E121, "Hig")</f>
         <v>0</v>
       </c>
-      <c r="D209" s="23" t="s">
+      <c r="D209" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E209" s="23">
+      <c r="E209" s="21">
         <v>4</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D210" s="23" t="s">
+      <c r="D210" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="E210" s="23">
+      <c r="E210" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D211" s="26" t="s">
+      <c r="D211" s="24" t="s">
         <v>228</v>
       </c>
-      <c r="E211" s="26"/>
+      <c r="E211" s="24"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A212" s="23" t="s">
+      <c r="A212" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="B212" s="23">
+      <c r="B212" s="21">
         <f>COUNTIFS( B2:B121, "Indian", I2:I121, "D")</f>
         <v>12</v>
       </c>
-      <c r="D212" s="26" t="s">
+      <c r="D212" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E212" s="26">
+      <c r="E212" s="24">
         <v>4</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D213" s="26" t="s">
+      <c r="D213" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E213" s="26">
+      <c r="E213" s="24">
         <v>4</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D214" s="26" t="s">
+      <c r="D214" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E214" s="26">
+      <c r="E214" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A215" s="21" t="s">
+      <c r="A215" s="19" t="s">
         <v>222</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D215" s="25" t="s">
+      <c r="D215" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="E215" s="25"/>
+      <c r="E215" s="23"/>
     </row>
     <row r="216" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A216" s="21" t="s">
+      <c r="A216" s="19" t="s">
         <v>217</v>
       </c>
       <c r="B216" s="1">
         <f>COUNTIFS( B2:B121, "Indian", I2:I121, "D", H2:H121, "True", E2:E121, "Low")</f>
         <v>4</v>
       </c>
-      <c r="D216" s="25" t="s">
+      <c r="D216" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="E216" s="25">
+      <c r="E216" s="23">
         <v>4</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A217" s="21" t="s">
+      <c r="A217" s="19" t="s">
         <v>218</v>
       </c>
       <c r="B217" s="1">
         <f>COUNTIFS( B2:B121, "Indian", I2:I121, "D", H2:H121, "True", E2:E121, "Mid")</f>
         <v>2</v>
       </c>
-      <c r="D217" s="25" t="s">
+      <c r="D217" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E217" s="25">
+      <c r="E217" s="23">
         <v>2</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A218" s="21" t="s">
+      <c r="A218" s="19" t="s">
         <v>219</v>
       </c>
       <c r="B218" s="1">
         <f>COUNTIFS( B2:B121, "Indian", I2:I121, "D", H2:H121, "True", E2:E121, "Hig")</f>
         <v>1</v>
       </c>
-      <c r="D218" s="25" t="s">
+      <c r="D218" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E218" s="25">
+      <c r="E218" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D219" s="27" t="s">
+      <c r="D219" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="E219" s="27"/>
+      <c r="E219" s="25"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D220" s="27" t="s">
+      <c r="D220" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="E220" s="27">
+      <c r="E220" s="25">
         <v>4</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A221" s="23" t="s">
+      <c r="A221" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B221" s="23">
+      <c r="B221" s="21">
         <f>COUNTIFS( B2:B121, "Latino", I2:I121, "D")</f>
         <v>12</v>
       </c>
-      <c r="D221" s="27" t="s">
+      <c r="D221" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="E221" s="27">
+      <c r="E221" s="25">
         <v>4</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D222" s="27" t="s">
+      <c r="D222" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E222" s="27">
+      <c r="E222" s="25">
         <v>0</v>
       </c>
     </row>
@@ -12420,10 +13067,10 @@
       <c r="B223" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D223" s="28" t="s">
+      <c r="D223" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="E223" s="28"/>
+      <c r="E223" s="26"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
@@ -12433,10 +13080,10 @@
         <f>COUNTIFS( B2:B121, "Latino", I2:I121, "D", H2:H121, "True", E2:E121, "Low")</f>
         <v>4</v>
       </c>
-      <c r="D224" s="28" t="s">
+      <c r="D224" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="E224" s="28">
+      <c r="E224" s="26">
         <v>2</v>
       </c>
     </row>
@@ -12448,10 +13095,10 @@
         <f>COUNTIFS( B2:B121, "Latino", I2:I121, "D", H2:H121, "True", E2:E121, "Mid")</f>
         <v>4</v>
       </c>
-      <c r="D225" s="28" t="s">
+      <c r="D225" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="E225" s="28">
+      <c r="E225" s="26">
         <v>1</v>
       </c>
     </row>
@@ -12463,18 +13110,18 @@
         <f>COUNTIFS( B2:B121, "Latino", I2:I121, "D", H2:H121, "True", E2:E121, "Hig")</f>
         <v>0</v>
       </c>
-      <c r="D226" s="28" t="s">
+      <c r="D226" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="E226" s="28">
+      <c r="E226" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A229" s="23" t="s">
+      <c r="A229" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B229" s="23">
+      <c r="B229" s="21">
         <f>COUNTIFS( B2:B121, "White", I2:I121, "D")</f>
         <v>12</v>
       </c>
@@ -12519,7 +13166,7 @@
       <c r="B235"/>
     </row>
     <row r="240" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A240" s="22" t="s">
+      <c r="A240" s="20" t="s">
         <v>234</v>
       </c>
     </row>
@@ -12550,7 +13197,7 @@
       </c>
     </row>
     <row r="261" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A261" s="22" t="s">
+      <c r="A261" s="20" t="s">
         <v>234</v>
       </c>
     </row>
@@ -12581,7 +13228,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J158" xr:uid="{8E937269-5730-0745-BDE6-3F3B154E2F73}"/>
+  <autoFilter ref="A1:J158" xr:uid="{8E937269-5730-0745-BDE6-3F3B154E2F73}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="D"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J121">
+    <sortCondition ref="G2:G121"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="A125:B126"/>
   </mergeCells>

--- a/DeepFace/Ergebnisse.xlsx
+++ b/DeepFace/Ergebnisse.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eldarakhundzada/Desktop/8. Semester/BachelorThesis/DeepFace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDEAEEFD-42EC-A74F-A5ED-79B1A81165EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1BE8E3-C2BB-A34C-99D0-8173068FC9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F8B601AC-B7A8-9541-AC5C-870221668981}"/>
+    <workbookView xWindow="-4680" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{F8B601AC-B7A8-9541-AC5C-870221668981}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$J$158</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="239">
   <si>
     <t>Ethnie</t>
   </si>
@@ -1016,7 +1017,7 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1176,6 +1177,52 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="brightRoom" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="flat">
+                <a:bevelT w="50800" h="101600" prst="angle"/>
+                <a:contourClr>
+                  <a:srgbClr val="000000"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="brightRoom" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="flat">
+                <a:bevelT w="50800" h="101600" prst="angle"/>
+                <a:contourClr>
+                  <a:srgbClr val="000000"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -1232,11 +1279,31 @@
           <c:cat>
             <c:strRef>
               <c:f>Tabelle1!$A$130:$A$131</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Erfolgreiche Moprhs:</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Fehlgeschlagene 
+Morphs:</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Tabelle1!$B$130:$B$131</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -1407,11 +1474,54 @@
           <c:cat>
             <c:strRef>
               <c:f>Tabelle1!$A$144:$A$149</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Low mit Erfolg</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Low ohne Erfolg</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mid mit Erfolg</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Mid ohne Erfolg</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Hig mit Erfolg</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Hig ohne Erfolg</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Tabelle1!$B$144:$B$149</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -8687,7 +8797,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E937269-5730-0745-BDE6-3F3B154E2F73}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J265"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -8727,236 +8836,236 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="4" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="4">
-        <v>260</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>194</v>
+      <c r="F2" s="3">
+        <v>101</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J2" s="4">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="I2" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="5">
-        <v>454</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>66</v>
+      <c r="F3" s="3">
+        <v>105</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="J3" s="5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="6">
-        <v>37</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>75</v>
+      <c r="J3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3">
+        <v>101</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J4" s="6">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="I4" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="6">
-        <v>759</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>185</v>
+      <c r="F5" s="3">
+        <v>578</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="J5" s="6">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="J5" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3">
+        <v>101</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J6" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="11">
+        <v>560</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="J7" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="6">
-        <v>330</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J6" s="6">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="12">
-        <v>273</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="J7" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="5">
-        <v>658</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>38</v>
+      <c r="F8" s="4">
+        <v>779</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J8" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I8" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J8" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>10</v>
@@ -8968,10 +9077,10 @@
         <v>12</v>
       </c>
       <c r="F9" s="4">
-        <v>129</v>
+        <v>273</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>15</v>
@@ -8980,47 +9089,47 @@
         <v>211</v>
       </c>
       <c r="J9" s="4">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="5">
-        <v>114</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>101</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="4">
+        <v>779</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J10" s="5">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I10" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J10" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>161</v>
+        <v>24</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>10</v>
@@ -9029,13 +9138,13 @@
         <v>26</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" s="4">
-        <v>603</v>
+        <v>56</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>165</v>
+        <v>30</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>15</v>
@@ -9044,111 +9153,111 @@
         <v>211</v>
       </c>
       <c r="J11" s="4">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="6">
-        <v>3</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>146</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="4">
+        <v>779</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J12" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="12">
+        <v>241</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="J12" s="6">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="11" t="s">
+      <c r="J13" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="11">
-        <v>161</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="J13" s="11">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="3">
-        <v>105</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>17</v>
+      <c r="F14" s="5">
+        <v>7</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J14" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I14" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J14" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>36</v>
@@ -9157,13 +9266,13 @@
         <v>11</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" s="5">
-        <v>168</v>
+        <v>658</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>15</v>
@@ -9172,175 +9281,175 @@
         <v>211</v>
       </c>
       <c r="J15" s="5">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="4">
-        <v>778</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>167</v>
+      <c r="F16" s="5">
+        <v>7</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J16" s="4">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="I16" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J16" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="3">
-        <v>604</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>57</v>
+      <c r="E17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="5">
+        <v>746</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="5">
+        <v>7</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J18" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="13">
+        <v>25</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="J19" s="13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="E20" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="6">
-        <v>639</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J18" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="7">
-        <v>114</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="J19" s="7">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="3">
-        <v>264</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>59</v>
+      <c r="F20" s="6">
+        <v>916</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J20" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I20" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="J20" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>36</v>
@@ -9349,13 +9458,13 @@
         <v>26</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" s="6">
-        <v>312</v>
+        <v>639</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>15</v>
@@ -9364,143 +9473,143 @@
         <v>211</v>
       </c>
       <c r="J21" s="6">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F22" s="3">
-        <v>879</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>158</v>
+      <c r="F22" s="6">
+        <v>916</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J22" s="3">
-        <v>100</v>
+      <c r="I22" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="J22" s="6">
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="A23" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="3">
-        <v>101</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>16</v>
+      <c r="C23" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="6">
+        <v>342</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="H23" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J23" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="6">
+        <v>916</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J23" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="J24" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E25" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="5">
-        <v>119</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J24" s="5">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="11">
-        <v>164</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>84</v>
+      <c r="F25" s="7">
+        <v>400</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="H25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="J25" s="11">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I25" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="J25" s="7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>10</v>
@@ -9509,62 +9618,62 @@
         <v>11</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F26" s="3">
-        <v>578</v>
+        <v>253</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J26" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="5">
-        <v>240</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>138</v>
+      <c r="F27" s="3">
+        <v>604</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="I27" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="J27" s="5">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J27" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>10</v>
@@ -9576,187 +9685,187 @@
         <v>13</v>
       </c>
       <c r="F28" s="3">
-        <v>361</v>
+        <v>253</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J28" s="3">
-        <v>76</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="A29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="6">
-        <v>777</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>145</v>
+      <c r="E29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="3">
+        <v>264</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J29" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="3">
+        <v>253</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J29" s="6">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="J30" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="5" t="s">
+      <c r="C31" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="5">
-        <v>17</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J30" s="5">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="12">
-        <v>779</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>27</v>
+      <c r="E31" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="11">
+        <v>482</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I31" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="J31" s="12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="I31" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="J31" s="11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="3" t="s">
+      <c r="D32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="3">
-        <v>81</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>120</v>
+      <c r="F32" s="4">
+        <v>471</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J32" s="3">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="5">
-        <v>362</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>176</v>
+      <c r="I32" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J32" s="4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="4">
+        <v>260</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="I33" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="5">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J33" s="4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>90</v>
+        <v>192</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>10</v>
@@ -9765,30 +9874,30 @@
         <v>26</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F34" s="4">
-        <v>181</v>
+        <v>471</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J34" s="4">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>10</v>
@@ -9800,10 +9909,10 @@
         <v>13</v>
       </c>
       <c r="F35" s="4">
-        <v>398</v>
+        <v>579</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>131</v>
+        <v>235</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>15</v>
@@ -9812,175 +9921,175 @@
         <v>211</v>
       </c>
       <c r="J35" s="4">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" s="4">
+        <v>471</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J36" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="12">
+        <v>300</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="J37" s="12">
         <v>36</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="6">
-        <v>342</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J36" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="13" t="s">
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D38" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="13">
-        <v>746</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="J37" s="13">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F38" s="3">
-        <v>253</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>56</v>
+      <c r="F38" s="5">
+        <v>17</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J38" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" s="6" t="s">
+      <c r="J38" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="6">
-        <v>684</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>79</v>
+      <c r="D39" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="5">
+        <v>454</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I39" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J39" s="6">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" s="3" t="s">
+      <c r="J39" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="3" t="s">
+      <c r="C40" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40" s="3">
-        <v>482</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>61</v>
+      <c r="E40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="5">
+        <v>17</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J40" s="3">
-        <v>30</v>
+      <c r="I40" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J40" s="5">
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>36</v>
@@ -9989,86 +10098,86 @@
         <v>11</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" s="5">
-        <v>104</v>
+        <v>440</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J41" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" s="5">
+        <v>17</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J41" s="5">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="4">
-        <v>779</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J42" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="12">
-        <v>223</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="12" t="s">
+      <c r="J42" s="5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="13">
+        <v>672</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H43" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="J43" s="12">
-        <v>58</v>
+      <c r="J43" s="13">
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -10103,12 +10212,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>181</v>
+        <v>71</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>36</v>
@@ -10117,13 +10226,13 @@
         <v>26</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F45" s="6">
-        <v>729</v>
+        <v>37</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>187</v>
+        <v>75</v>
       </c>
       <c r="H45" s="8" t="s">
         <v>15</v>
@@ -10132,15 +10241,15 @@
         <v>211</v>
       </c>
       <c r="J45" s="6">
-        <v>120</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>36</v>
@@ -10149,13 +10258,13 @@
         <v>26</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F46" s="6">
-        <v>212</v>
+        <v>322</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="H46" s="8" t="s">
         <v>15</v>
@@ -10164,268 +10273,268 @@
         <v>212</v>
       </c>
       <c r="J46" s="6">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C47" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="5">
-        <v>824</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>139</v>
+      <c r="F47" s="6">
+        <v>312</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I47" s="5" t="s">
+      <c r="I47" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="J47" s="5">
-        <v>88</v>
+      <c r="J47" s="6">
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="4" t="s">
+      <c r="A48" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="4">
-        <v>182</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I48" s="4" t="s">
+      <c r="E48" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" s="6">
+        <v>322</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J48" s="4">
+      <c r="J48" s="6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" s="7">
+        <v>684</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="11">
-        <v>173</v>
-      </c>
-      <c r="G49" s="11" t="s">
-        <v>87</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="J49" s="11">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D50" s="6" t="s">
+      <c r="J49" s="7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="6">
-        <v>274</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>148</v>
+      <c r="E50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="3">
+        <v>164</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I50" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J50" s="6">
-        <v>94</v>
+      <c r="I50" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J50" s="3">
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" s="5" t="s">
+      <c r="A51" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E51" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F51" s="5">
-        <v>7</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>37</v>
+      <c r="F51" s="3">
+        <v>161</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J51" s="5">
+      <c r="I51" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J51" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="6">
-        <v>371</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>182</v>
+      <c r="F52" s="3">
+        <v>164</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="I52" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J52" s="6">
-        <v>115</v>
+      <c r="J52" s="3">
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" s="4" t="s">
+      <c r="A53" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E53" s="4" t="s">
+      <c r="D53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="4">
-        <v>471</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>197</v>
+      <c r="F53" s="3">
+        <v>173</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="H53" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I53" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J53" s="4">
-        <v>33</v>
+      <c r="I53" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J53" s="3">
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B54" s="4" t="s">
+      <c r="A54" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="4">
-        <v>190</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>199</v>
+      <c r="D54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" s="3">
+        <v>164</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="H54" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="I54" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J54" s="4">
-        <v>55</v>
+      <c r="J54" s="3">
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>83</v>
@@ -10437,190 +10546,190 @@
         <v>11</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F55" s="11">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>15</v>
+        <v>89</v>
+      </c>
+      <c r="H55" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J55" s="11">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A56" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="6">
-        <v>777</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>147</v>
+      <c r="A56" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="4">
+        <v>190</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="H56" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="I56" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J56" s="6">
-        <v>93</v>
+      <c r="J56" s="4">
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A57" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D57" s="5" t="s">
+      <c r="A57" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F57" s="5">
-        <v>31</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>137</v>
+      <c r="F57" s="4">
+        <v>181</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="H57" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I57" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J57" s="5">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C58" s="3" t="s">
+      <c r="I57" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J57" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" s="3">
-        <v>281</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>160</v>
+      <c r="D58" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="4">
+        <v>190</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="H58" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J58" s="3">
-        <v>102</v>
+      <c r="I58" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J58" s="4">
+        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C59" s="3" t="s">
+      <c r="A59" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="3" t="s">
+      <c r="D59" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F59" s="3">
-        <v>253</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>58</v>
+      <c r="F59" s="4">
+        <v>223</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="H59" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I59" s="3" t="s">
+      <c r="I59" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J59" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" s="4">
+        <v>190</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J59" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F60" s="5">
-        <v>717</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J60" s="5">
-        <v>66</v>
+      <c r="J60" s="4">
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
-        <v>191</v>
+        <v>92</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>10</v>
@@ -10629,126 +10738,126 @@
         <v>26</v>
       </c>
       <c r="E61" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F61" s="12">
+        <v>138</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="J61" s="12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A62" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="12">
-        <v>471</v>
-      </c>
-      <c r="G61" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="J61" s="12">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="4">
-        <v>579</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>235</v>
+      <c r="F62" s="5">
+        <v>104</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="H62" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I62" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J62" s="4">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" s="4">
-        <v>239</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>169</v>
+      <c r="I62" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J62" s="5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A63" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="5">
+        <v>114</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="H63" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="I63" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="J63" s="4">
-        <v>108</v>
+      <c r="J63" s="5">
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A64" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" s="4">
-        <v>515</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I64" s="4" t="s">
+      <c r="A64" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="5">
+        <v>104</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J64" s="4">
-        <v>103</v>
+      <c r="J64" s="5">
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>36</v>
@@ -10760,27 +10869,27 @@
         <v>13</v>
       </c>
       <c r="F65" s="5">
-        <v>7</v>
+        <v>168</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="H65" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J65" s="5">
-        <v>15</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>36</v>
@@ -10789,62 +10898,62 @@
         <v>11</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F66" s="5">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>15</v>
+        <v>104</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>212</v>
       </c>
       <c r="J66" s="5">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A67" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="12">
-        <v>182</v>
-      </c>
-      <c r="G67" s="12" t="s">
-        <v>130</v>
+      <c r="A67" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" s="13">
+        <v>717</v>
+      </c>
+      <c r="G67" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I67" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="J67" s="12">
-        <v>81</v>
+      <c r="I67" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="J67" s="13">
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>36</v>
@@ -10856,10 +10965,10 @@
         <v>12</v>
       </c>
       <c r="F68" s="6">
-        <v>916</v>
+        <v>212</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="H68" s="8" t="s">
         <v>15</v>
@@ -10868,556 +10977,556 @@
         <v>212</v>
       </c>
       <c r="J68" s="6">
-        <v>19</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A69" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="3" t="s">
+      <c r="A69" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F69" s="3">
-        <v>174</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>119</v>
+      <c r="F69" s="6">
+        <v>114</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="H69" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I69" s="3" t="s">
+      <c r="I69" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J69" s="6">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A70" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="6">
         <v>212</v>
       </c>
-      <c r="J69" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" s="4" t="s">
+      <c r="G70" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="J70" s="6">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A71" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D71" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E70" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F70" s="4">
-        <v>186</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I70" s="4" t="s">
+      <c r="E71" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="6">
+        <v>146</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="J70" s="4">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F71" s="5">
-        <v>793</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="H71" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J71" s="5">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J71" s="6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>14</v>
       </c>
       <c r="F72" s="6">
+        <v>212</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="J72" s="6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A73" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B73" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G72" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J72" s="6">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="11">
-        <v>802</v>
-      </c>
-      <c r="G73" s="11" t="s">
-        <v>156</v>
+      <c r="C73" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" s="7">
+        <v>183</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I73" s="11" t="s">
+      <c r="I73" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="J73" s="11">
-        <v>98</v>
+      <c r="J73" s="7">
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A74" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="6">
-        <v>322</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>76</v>
+      <c r="A74" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" s="3">
+        <v>174</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="H74" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I74" s="6" t="s">
+      <c r="I74" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J74" s="6">
-        <v>45</v>
+      <c r="J74" s="3">
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A75" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" s="4" t="s">
+      <c r="A75" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F75" s="4">
-        <v>190</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>93</v>
+      <c r="D75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" s="3">
+        <v>81</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="H75" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I75" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J75" s="4">
-        <v>57</v>
+      <c r="I75" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J75" s="3">
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A76" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E76" s="6" t="s">
+      <c r="A76" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F76" s="6">
-        <v>916</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>48</v>
+      <c r="F76" s="3">
+        <v>174</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="H76" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I76" s="6" t="s">
+      <c r="I76" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J76" s="6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C77" s="4" t="s">
+      <c r="J76" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A77" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D77" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E77" s="4" t="s">
+      <c r="D77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F77" s="4">
-        <v>56</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>30</v>
+      <c r="F77" s="3">
+        <v>361</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="H77" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I77" s="4" t="s">
+      <c r="I77" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="J77" s="4">
+      <c r="J77" s="3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A78" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" s="3">
+        <v>174</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J78" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A79" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" s="11">
+        <v>650</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="H79" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I79" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="J79" s="11">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E78" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F78" s="6">
-        <v>400</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H78" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J78" s="6">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A79" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E79" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F79" s="12">
-        <v>779</v>
-      </c>
-      <c r="G79" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I79" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="J79" s="12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A80" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="3">
-        <v>101</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>18</v>
+      <c r="E80" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="4">
+        <v>182</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="H80" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I80" s="3" t="s">
+      <c r="I80" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J80" s="3">
-        <v>3</v>
+      <c r="J80" s="4">
+        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A81" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B81" s="3" t="s">
+      <c r="A81" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="3">
-        <v>174</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>121</v>
+      <c r="D81" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="4">
+        <v>129</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="H81" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J81" s="3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D82" s="6" t="s">
+      <c r="I81" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J81" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A82" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E82" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F82" s="6">
-        <v>183</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>114</v>
+      <c r="E82" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="4">
+        <v>182</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="H82" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I82" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J82" s="6">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F83" s="5">
-        <v>374</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>174</v>
+      <c r="I82" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J82" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="4">
+        <v>398</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="H83" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I83" s="5" t="s">
+      <c r="I83" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="J83" s="5">
-        <v>110</v>
+      <c r="J83" s="4">
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A84" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F84" s="5">
-        <v>369</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="H84" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" s="5" t="s">
+      <c r="A84" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84" s="4">
+        <v>182</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J84" s="5">
-        <v>111</v>
+      <c r="J84" s="4">
+        <v>83</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A85" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C85" s="11" t="s">
+      <c r="A85" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C85" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D85" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E85" s="11" t="s">
+      <c r="D85" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E85" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F85" s="11">
-        <v>164</v>
-      </c>
-      <c r="G85" s="11" t="s">
-        <v>88</v>
+      <c r="F85" s="12">
+        <v>186</v>
+      </c>
+      <c r="G85" s="12" t="s">
+        <v>132</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I85" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="J85" s="11">
-        <v>53</v>
+      <c r="I85" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="J85" s="12">
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>118</v>
@@ -11429,13 +11538,13 @@
         <v>26</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F86" s="5">
         <v>31</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>15</v>
@@ -11444,30 +11553,30 @@
         <v>212</v>
       </c>
       <c r="J86" s="5">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>55</v>
+        <v>118</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F87" s="5">
-        <v>440</v>
+        <v>240</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="H87" s="8" t="s">
         <v>15</v>
@@ -11476,204 +11585,204 @@
         <v>211</v>
       </c>
       <c r="J87" s="5">
-        <v>40</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A88" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C88" s="6" t="s">
+      <c r="A88" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C88" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E88" s="6" t="s">
+      <c r="E88" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F88" s="6">
-        <v>371</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="H88" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I88" s="6" t="s">
+      <c r="F88" s="5">
+        <v>31</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J88" s="6">
-        <v>117</v>
+      <c r="J88" s="5">
+        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>9</v>
+        <v>118</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E89" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="5">
+        <v>824</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J89" s="5">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A90" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E90" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F89" s="5">
-        <v>7</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I89" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J89" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F90" s="3">
-        <v>650</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>124</v>
+      <c r="F90" s="5">
+        <v>31</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="H90" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="I90" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J90" s="5">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A91" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91" s="13">
+        <v>119</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="J90" s="3">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A91" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C91" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D91" s="11" t="s">
+      <c r="J91" s="13">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A92" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E91" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F91" s="11">
-        <v>101</v>
-      </c>
-      <c r="G91" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H91" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I91" s="11" t="s">
+      <c r="E92" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92" s="6">
+        <v>777</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J91" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A92" s="4" t="s">
+      <c r="J92" s="6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A93" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" s="6">
+        <v>3</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J93" s="6">
         <v>92</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F92" s="4">
-        <v>190</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H92" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I92" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J92" s="4">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F93" s="4">
-        <v>300</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I93" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J93" s="4">
-        <v>36</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>118</v>
@@ -11685,123 +11794,123 @@
         <v>11</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F94" s="6">
         <v>777</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>20</v>
+        <v>147</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="I94" s="6" t="s">
         <v>212</v>
       </c>
       <c r="J94" s="6">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A95" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E95" s="4" t="s">
+      <c r="A95" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F95" s="4">
-        <v>515</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J95" s="4">
-        <v>105</v>
+      <c r="F95" s="6">
+        <v>274</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J95" s="6">
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A96" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B96" s="3" t="s">
+      <c r="A96" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B96" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D96" s="3" t="s">
+      <c r="C96" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D96" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E96" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F96" s="3">
-        <v>174</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>123</v>
+      <c r="F96" s="6">
+        <v>777</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="H96" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="I96" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="J96" s="3">
-        <v>77</v>
+      <c r="J96" s="6">
+        <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A97" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B97" s="13" t="s">
+      <c r="A97" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F97" s="7">
         <v>83</v>
       </c>
-      <c r="C97" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D97" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F97" s="13">
-        <v>104</v>
-      </c>
-      <c r="G97" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H97" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I97" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="J97" s="13">
-        <v>63</v>
+      <c r="G97" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="J97" s="7">
+        <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>154</v>
@@ -11813,13 +11922,13 @@
         <v>11</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F98" s="3">
         <v>813</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H98" s="9" t="s">
         <v>20</v>
@@ -11828,47 +11937,47 @@
         <v>212</v>
       </c>
       <c r="J98" s="3">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A99" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C99" s="4" t="s">
+      <c r="A99" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F99" s="4">
-        <v>471</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I99" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J99" s="4">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D99" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" s="3">
+        <v>802</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J99" s="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>10</v>
@@ -11877,278 +11986,278 @@
         <v>11</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F100" s="3">
-        <v>177</v>
+        <v>813</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="H100" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I100" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J100" s="3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A101" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="3">
+        <v>879</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I101" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="J100" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D101" s="5" t="s">
+      <c r="J101" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A102" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E101" s="5" t="s">
+      <c r="E102" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F101" s="5">
-        <v>672</v>
-      </c>
-      <c r="G101" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I101" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J101" s="5">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A102" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F102" s="5">
-        <v>17</v>
-      </c>
-      <c r="G102" s="5" t="s">
-        <v>69</v>
+      <c r="F102" s="3">
+        <v>813</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>159</v>
       </c>
       <c r="H102" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I102" s="5" t="s">
+      <c r="I102" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J102" s="5">
-        <v>41</v>
+      <c r="J102" s="3">
+        <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A103" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B103" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C103" s="12" t="s">
+      <c r="A103" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C103" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D103" s="12" t="s">
+      <c r="D103" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103" s="11">
+        <v>281</v>
+      </c>
+      <c r="G103" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I103" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="J103" s="11">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A104" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E103" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F103" s="12">
-        <v>182</v>
-      </c>
-      <c r="G103" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="H103" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I103" s="12" t="s">
+      <c r="E104" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F104" s="4">
+        <v>515</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H104" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I104" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J103" s="12">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A104" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B104" s="3" t="s">
+      <c r="J104" s="4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A105" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B105" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C105" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D104" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="3" t="s">
+      <c r="D105" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E105" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F104" s="3">
-        <v>813</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H104" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J104" s="3">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A105" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D105" s="6" t="s">
+      <c r="F105" s="4">
+        <v>603</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H105" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="J105" s="4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A106" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E105" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F105" s="6">
-        <v>916</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="J105" s="6">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F106" s="3">
-        <v>560</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>22</v>
+      <c r="E106" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="4">
+        <v>515</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I106" s="3" t="s">
+      <c r="I106" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J106" s="4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A107" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="4">
+        <v>778</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I107" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="J106" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E107" s="5" t="s">
+      <c r="J107" s="4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A108" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E108" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F107" s="5">
-        <v>25</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I107" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="J107" s="5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A108" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E108" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F108" s="5">
-        <v>369</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>177</v>
+      <c r="F108" s="4">
+        <v>515</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="H108" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I108" s="5" t="s">
+      <c r="I108" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J108" s="5">
-        <v>113</v>
+      <c r="J108" s="4">
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.2">
@@ -12168,19 +12277,19 @@
         <v>14</v>
       </c>
       <c r="F109" s="12">
-        <v>515</v>
+        <v>239</v>
       </c>
       <c r="G109" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="H109" s="14" t="s">
-        <v>20</v>
+        <v>169</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="I109" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J109" s="12">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
@@ -12216,232 +12325,232 @@
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A111" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B111" s="3" t="s">
+      <c r="A111" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D111" s="3" t="s">
+      <c r="C111" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D111" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E111" s="3" t="s">
+      <c r="E111" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" s="5">
+        <v>374</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H111" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J111" s="5">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A112" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" s="5">
+        <v>369</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H112" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J112" s="5">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A113" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="5">
+        <v>362</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H113" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I113" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J113" s="5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A114" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F111" s="3">
-        <v>813</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J111" s="3">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F112" s="4">
-        <v>138</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H112" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I112" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J112" s="4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E113" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F113" s="4">
-        <v>241</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I113" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="J113" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A114" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F114" s="6">
-        <v>322</v>
-      </c>
-      <c r="G114" s="6" t="s">
-        <v>78</v>
+      <c r="F114" s="5">
+        <v>369</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>177</v>
       </c>
       <c r="H114" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I114" s="6" t="s">
+      <c r="I114" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J114" s="6">
-        <v>47</v>
+      <c r="J114" s="5">
+        <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A115" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C115" s="7" t="s">
+      <c r="A115" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C115" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D115" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F115" s="13">
+        <v>793</v>
+      </c>
+      <c r="G115" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I115" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="J115" s="13">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A116" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D116" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E115" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F115" s="7">
+      <c r="E116" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F116" s="6">
+        <v>371</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I116" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="G115" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="H115" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I115" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="J115" s="7">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A116" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F116" s="3">
-        <v>253</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H116" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J116" s="3">
-        <v>29</v>
+      <c r="J116" s="6">
+        <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A117" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C117" s="5" t="s">
+      <c r="A117" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C117" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D117" s="5" t="s">
+      <c r="D117" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E117" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F117" s="5">
-        <v>31</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I117" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J117" s="5">
-        <v>89</v>
+      <c r="E117" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" s="6">
+        <v>330</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I117" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J117" s="6">
+        <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>154</v>
@@ -12453,13 +12562,13 @@
         <v>26</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F118" s="6">
         <v>371</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H118" s="9" t="s">
         <v>20</v>
@@ -12468,47 +12577,47 @@
         <v>212</v>
       </c>
       <c r="J118" s="6">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A119" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C119" s="5" t="s">
+      <c r="A119" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C119" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D119" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F119" s="5">
-        <v>104</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I119" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J119" s="5">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D119" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F119" s="6">
+        <v>759</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I119" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J119" s="6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="6" t="s">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>36</v>
@@ -12517,30 +12626,30 @@
         <v>26</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F120" s="6">
-        <v>146</v>
+        <v>371</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="H120" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J120" s="6">
-        <v>70</v>
+        <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="7" t="s">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>36</v>
@@ -12549,47 +12658,43 @@
         <v>26</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F121" s="7">
-        <v>212</v>
+        <v>729</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H121" s="14" t="s">
-        <v>20</v>
+        <v>187</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J121" s="7">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="27" t="s">
         <v>201</v>
       </c>
       <c r="B125" s="27"/>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="27"/>
       <c r="B126" s="27"/>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="17" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="129" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" s="16"/>
     </row>
-    <row r="130" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="16" t="s">
         <v>203</v>
       </c>
@@ -12598,7 +12703,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A131" s="15" t="s">
         <v>204</v>
       </c>
@@ -12607,23 +12712,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="132" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="133" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="134" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="135" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="136" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="137" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="138" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="139" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="140" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="18" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="141" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="142" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="143" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="144" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>207</v>
       </c>
@@ -12632,7 +12726,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="145" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
         <v>206</v>
       </c>
@@ -12641,7 +12735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>208</v>
       </c>
@@ -12650,7 +12744,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="147" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>209</v>
       </c>
@@ -12659,7 +12753,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>215</v>
       </c>
@@ -12668,7 +12762,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="149" spans="1:2" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>216</v>
       </c>
@@ -12677,19 +12771,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="150" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="151" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="152" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="153" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="154" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="155" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="156" spans="1:2" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A156" s="20" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="157" spans="1:2" hidden="1" x14ac:dyDescent="0.2"/>
-    <row r="158" spans="1:2" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A158" s="22" t="s">
         <v>214</v>
       </c>
@@ -13228,15 +13315,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J158" xr:uid="{8E937269-5730-0745-BDE6-3F3B154E2F73}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="D"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J158" xr:uid="{8E937269-5730-0745-BDE6-3F3B154E2F73}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J121">
-    <sortCondition ref="G2:G121"/>
+    <sortCondition ref="J2:J121"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A125:B126"/>
@@ -13257,4 +13338,142 @@
     <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544D36A3-C0DE-A24A-AFE4-0E637A0F7FD3}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3">
+        <v>578</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J1" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3">
+        <v>101</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J2" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="11">
+        <v>101</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="J3" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3">
+        <v>560</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J4" s="3">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/DeepFace/Ergebnisse.xlsx
+++ b/DeepFace/Ergebnisse.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eldarakhundzada/Desktop/8. Semester/BachelorThesis/DeepFace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1BE8E3-C2BB-A34C-99D0-8173068FC9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA85D6DD-C5BF-FF4F-9B2E-55D0D18C8F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4680" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{F8B601AC-B7A8-9541-AC5C-870221668981}"/>
+    <workbookView xWindow="-4680" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{F8B601AC-B7A8-9541-AC5C-870221668981}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$J$158</definedName>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="240">
   <si>
     <t>Ethnie</t>
   </si>
@@ -767,6 +766,9 @@
   <si>
     <t>Unterschiedlicher 
 Hintergrund</t>
+  </si>
+  <si>
+    <t>Test</t>
   </si>
 </sst>
 </file>
@@ -1014,10 +1016,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1199,6 +1201,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-D460-2F44-9E20-60D4AEB5EC87}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1222,6 +1229,11 @@
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-D460-2F44-9E20-60D4AEB5EC87}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -8797,14 +8809,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E937269-5730-0745-BDE6-3F3B154E2F73}">
-  <dimension ref="A1:J265"/>
+  <dimension ref="A1:K265"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="8" width="18.83203125" style="1"/>
     <col min="10" max="16384" width="18.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>189</v>
       </c>
@@ -8836,7 +8848,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -8867,8 +8879,11 @@
       <c r="J2" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K2" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -8900,7 +8915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
@@ -8932,7 +8947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -8964,7 +8979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -8996,7 +9011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>8</v>
       </c>
@@ -9028,7 +9043,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>23</v>
       </c>
@@ -9060,7 +9075,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9092,7 +9107,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
@@ -9124,7 +9139,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>24</v>
       </c>
@@ -9156,7 +9171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
@@ -9188,8 +9203,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="28" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="27" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="12" t="s">
@@ -9220,7 +9235,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>33</v>
       </c>
@@ -9252,7 +9267,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>33</v>
       </c>
@@ -9284,7 +9299,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>35</v>
       </c>
@@ -12677,14 +12692,14 @@
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A125" s="27" t="s">
+      <c r="A125" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="B125" s="27"/>
+      <c r="B125" s="28"/>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A126" s="27"/>
-      <c r="B126" s="27"/>
+      <c r="A126" s="28"/>
+      <c r="B126" s="28"/>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="17" t="s">
@@ -13338,142 +13353,4 @@
     <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544D36A3-C0DE-A24A-AFE4-0E637A0F7FD3}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="3">
-        <v>578</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J1" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3">
-        <v>101</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="J2" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="11">
-        <v>101</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="J3" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="3">
-        <v>560</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J4" s="3">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/DeepFace/Ergebnisse.xlsx
+++ b/DeepFace/Ergebnisse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eldarakhundzada/Desktop/8. Semester/BachelorThesis/DeepFace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA85D6DD-C5BF-FF4F-9B2E-55D0D18C8F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88277539-C3C7-3947-BE0E-A9B0A6408F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4680" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{F8B601AC-B7A8-9541-AC5C-870221668981}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="239">
   <si>
     <t>Ethnie</t>
   </si>
@@ -766,9 +766,6 @@
   <si>
     <t>Unterschiedlicher 
 Hintergrund</t>
-  </si>
-  <si>
-    <t>Test</t>
   </si>
 </sst>
 </file>
@@ -8809,14 +8806,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E937269-5730-0745-BDE6-3F3B154E2F73}">
-  <dimension ref="A1:K265"/>
+  <dimension ref="A1:J265"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="8" width="18.83203125" style="1"/>
     <col min="10" max="16384" width="18.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>189</v>
       </c>
@@ -8848,7 +8845,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -8879,11 +8876,8 @@
       <c r="J2" s="3">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -8915,7 +8909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>7</v>
       </c>
@@ -8947,7 +8941,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -8979,7 +8973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -9011,7 +9005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>8</v>
       </c>
@@ -9043,7 +9037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>23</v>
       </c>
@@ -9075,7 +9069,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9107,7 +9101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
@@ -9139,7 +9133,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>24</v>
       </c>
@@ -9171,7 +9165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
@@ -9203,7 +9197,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="27" t="s">
         <v>25</v>
       </c>
@@ -9235,7 +9229,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>33</v>
       </c>
@@ -9267,7 +9261,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>33</v>
       </c>
@@ -9299,7 +9293,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>35</v>
       </c>

--- a/DeepFace/Ergebnisse.xlsx
+++ b/DeepFace/Ergebnisse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eldarakhundzada/Desktop/8. Semester/BachelorThesis/DeepFace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88277539-C3C7-3947-BE0E-A9B0A6408F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82DD4F0-2C5D-6F44-B944-5825BE90F49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4680" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{F8B601AC-B7A8-9541-AC5C-870221668981}"/>
+    <workbookView xWindow="-4680" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{F8B601AC-B7A8-9541-AC5C-870221668981}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="238">
   <si>
     <t>Ethnie</t>
   </si>
@@ -224,12 +224,6 @@
     <t>0.131</t>
   </si>
   <si>
-    <t>0.4904</t>
-  </si>
-  <si>
-    <t>0.169</t>
-  </si>
-  <si>
     <t>IM17-low.png</t>
   </si>
   <si>
@@ -296,12 +290,6 @@
     <t>Indian</t>
   </si>
   <si>
-    <t>0.139</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
     <t>0.1946</t>
   </si>
   <si>
@@ -417,33 +405,6 @@
   </si>
   <si>
     <t>0.3077</t>
-  </si>
-  <si>
-    <t>IM182-low.png</t>
-  </si>
-  <si>
-    <t>IM182-mid.png</t>
-  </si>
-  <si>
-    <t>IM182-hig.png</t>
-  </si>
-  <si>
-    <t>0.1755</t>
-  </si>
-  <si>
-    <t>0.0937</t>
-  </si>
-  <si>
-    <t>0.2271</t>
-  </si>
-  <si>
-    <t>0.1491</t>
-  </si>
-  <si>
-    <t>0.244</t>
-  </si>
-  <si>
-    <t>0.3834</t>
   </si>
   <si>
     <t>IM31-low.png</t>
@@ -766,6 +727,42 @@
   <si>
     <t>Unterschiedlicher 
 Hintergrund</t>
+  </si>
+  <si>
+    <t>0.1266</t>
+  </si>
+  <si>
+    <t>0.1073</t>
+  </si>
+  <si>
+    <t>0.4691</t>
+  </si>
+  <si>
+    <t>0.208</t>
+  </si>
+  <si>
+    <t>IM129-hig.png</t>
+  </si>
+  <si>
+    <t>IM129-mid.png</t>
+  </si>
+  <si>
+    <t>IM129-low.png</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>0.3869</t>
+  </si>
+  <si>
+    <t>0.2348</t>
+  </si>
+  <si>
+    <t>0.1769</t>
+  </si>
+  <si>
+    <t>0.1411</t>
   </si>
 </sst>
 </file>
@@ -8815,7 +8812,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -8827,7 +8824,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -8839,10 +8836,10 @@
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -8871,7 +8868,7 @@
         <v>15</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J2" s="3">
         <v>1</v>
@@ -8903,7 +8900,7 @@
         <v>15</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J3" s="3">
         <v>2</v>
@@ -8935,7 +8932,7 @@
         <v>15</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J4" s="3">
         <v>3</v>
@@ -8967,7 +8964,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J5" s="3">
         <v>4</v>
@@ -8999,7 +8996,7 @@
         <v>20</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J6" s="3">
         <v>5</v>
@@ -9031,7 +9028,7 @@
         <v>20</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J7" s="11">
         <v>6</v>
@@ -9063,7 +9060,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J8" s="4">
         <v>7</v>
@@ -9095,7 +9092,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J9" s="4">
         <v>8</v>
@@ -9127,7 +9124,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J10" s="4">
         <v>9</v>
@@ -9159,7 +9156,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J11" s="4">
         <v>10</v>
@@ -9191,7 +9188,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J12" s="4">
         <v>11</v>
@@ -9223,7 +9220,7 @@
         <v>20</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J13" s="12">
         <v>12</v>
@@ -9255,7 +9252,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J14" s="5">
         <v>13</v>
@@ -9287,7 +9284,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J15" s="5">
         <v>14</v>
@@ -9319,7 +9316,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J16" s="5">
         <v>15</v>
@@ -9351,7 +9348,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J17" s="5">
         <v>16</v>
@@ -9383,7 +9380,7 @@
         <v>20</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J18" s="5">
         <v>17</v>
@@ -9415,7 +9412,7 @@
         <v>20</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J19" s="13">
         <v>18</v>
@@ -9447,7 +9444,7 @@
         <v>15</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J20" s="6">
         <v>19</v>
@@ -9479,7 +9476,7 @@
         <v>15</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J21" s="6">
         <v>20</v>
@@ -9511,7 +9508,7 @@
         <v>15</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J22" s="6">
         <v>21</v>
@@ -9543,7 +9540,7 @@
         <v>15</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J23" s="6">
         <v>22</v>
@@ -9575,7 +9572,7 @@
         <v>20</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J24" s="6">
         <v>23</v>
@@ -9607,7 +9604,7 @@
         <v>15</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J25" s="7">
         <v>24</v>
@@ -9639,7 +9636,7 @@
         <v>15</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J26" s="3">
         <v>25</v>
@@ -9671,7 +9668,7 @@
         <v>15</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J27" s="3">
         <v>26</v>
@@ -9703,7 +9700,7 @@
         <v>15</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J28" s="3">
         <v>27</v>
@@ -9735,7 +9732,7 @@
         <v>15</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J29" s="3">
         <v>28</v>
@@ -9761,13 +9758,13 @@
         <v>253</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>60</v>
+        <v>228</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J30" s="3">
         <v>29</v>
@@ -9790,16 +9787,16 @@
         <v>14</v>
       </c>
       <c r="F31" s="11">
-        <v>482</v>
+        <v>270</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>61</v>
+        <v>229</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J31" s="11">
         <v>30</v>
@@ -9807,7 +9804,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>55</v>
@@ -9825,13 +9822,13 @@
         <v>471</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J32" s="4">
         <v>31</v>
@@ -9839,7 +9836,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>55</v>
@@ -9857,13 +9854,13 @@
         <v>260</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J33" s="4">
         <v>32</v>
@@ -9871,7 +9868,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>55</v>
@@ -9889,13 +9886,13 @@
         <v>471</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J34" s="4">
         <v>33</v>
@@ -9903,7 +9900,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>55</v>
@@ -9921,13 +9918,13 @@
         <v>579</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J35" s="4">
         <v>34</v>
@@ -9935,7 +9932,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>55</v>
@@ -9953,13 +9950,13 @@
         <v>471</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J36" s="4">
         <v>35</v>
@@ -9967,7 +9964,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>55</v>
@@ -9985,13 +9982,13 @@
         <v>300</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J37" s="12">
         <v>36</v>
@@ -9999,7 +9996,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>55</v>
@@ -10017,13 +10014,13 @@
         <v>17</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J38" s="5">
         <v>37</v>
@@ -10031,7 +10028,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>55</v>
@@ -10049,13 +10046,13 @@
         <v>454</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J39" s="5">
         <v>38</v>
@@ -10063,7 +10060,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>55</v>
@@ -10081,13 +10078,13 @@
         <v>17</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J40" s="5">
         <v>39</v>
@@ -10095,7 +10092,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>55</v>
@@ -10113,13 +10110,13 @@
         <v>440</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H41" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J41" s="5">
         <v>40</v>
@@ -10127,7 +10124,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>55</v>
@@ -10145,13 +10142,13 @@
         <v>17</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J42" s="5">
         <v>41</v>
@@ -10159,7 +10156,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>55</v>
@@ -10177,13 +10174,13 @@
         <v>672</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H43" s="14" t="s">
         <v>20</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J43" s="13">
         <v>42</v>
@@ -10191,7 +10188,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>55</v>
@@ -10209,13 +10206,13 @@
         <v>322</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H44" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J44" s="6">
         <v>43</v>
@@ -10223,7 +10220,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>55</v>
@@ -10241,13 +10238,13 @@
         <v>37</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H45" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J45" s="6">
         <v>44</v>
@@ -10255,7 +10252,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>55</v>
@@ -10273,13 +10270,13 @@
         <v>322</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H46" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J46" s="6">
         <v>45</v>
@@ -10287,7 +10284,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>55</v>
@@ -10305,13 +10302,13 @@
         <v>312</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J47" s="6">
         <v>46</v>
@@ -10319,7 +10316,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>55</v>
@@ -10337,13 +10334,13 @@
         <v>322</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H48" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J48" s="6">
         <v>47</v>
@@ -10351,7 +10348,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>55</v>
@@ -10369,13 +10366,13 @@
         <v>684</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J49" s="7">
         <v>48</v>
@@ -10383,10 +10380,10 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>10</v>
@@ -10401,13 +10398,13 @@
         <v>164</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>84</v>
+        <v>226</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J50" s="3">
         <v>49</v>
@@ -10415,10 +10412,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>10</v>
@@ -10430,16 +10427,16 @@
         <v>12</v>
       </c>
       <c r="F51" s="3">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>85</v>
+        <v>227</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J51" s="3">
         <v>50</v>
@@ -10447,10 +10444,10 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>10</v>
@@ -10465,13 +10462,13 @@
         <v>164</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H52" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J52" s="3">
         <v>51</v>
@@ -10479,10 +10476,10 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>10</v>
@@ -10497,13 +10494,13 @@
         <v>173</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H53" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J53" s="3">
         <v>52</v>
@@ -10511,10 +10508,10 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>10</v>
@@ -10529,13 +10526,13 @@
         <v>164</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H54" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J54" s="3">
         <v>53</v>
@@ -10543,10 +10540,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>10</v>
@@ -10561,13 +10558,13 @@
         <v>177</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H55" s="14" t="s">
         <v>20</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J55" s="11">
         <v>54</v>
@@ -10575,10 +10572,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>10</v>
@@ -10593,13 +10590,13 @@
         <v>190</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="H56" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J56" s="4">
         <v>55</v>
@@ -10607,10 +10604,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>10</v>
@@ -10625,13 +10622,13 @@
         <v>181</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="H57" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J57" s="4">
         <v>56</v>
@@ -10639,10 +10636,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>10</v>
@@ -10657,13 +10654,13 @@
         <v>190</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H58" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J58" s="4">
         <v>57</v>
@@ -10671,10 +10668,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>10</v>
@@ -10689,13 +10686,13 @@
         <v>223</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H59" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J59" s="4">
         <v>58</v>
@@ -10703,10 +10700,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>10</v>
@@ -10721,13 +10718,13 @@
         <v>190</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H60" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J60" s="4">
         <v>59</v>
@@ -10735,10 +10732,10 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>10</v>
@@ -10753,13 +10750,13 @@
         <v>138</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H61" s="14" t="s">
         <v>20</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J61" s="12">
         <v>60</v>
@@ -10767,10 +10764,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>36</v>
@@ -10785,13 +10782,13 @@
         <v>104</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H62" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J62" s="5">
         <v>61</v>
@@ -10799,10 +10796,10 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>36</v>
@@ -10817,13 +10814,13 @@
         <v>114</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H63" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J63" s="5">
         <v>62</v>
@@ -10831,10 +10828,10 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>36</v>
@@ -10849,13 +10846,13 @@
         <v>104</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H64" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J64" s="5">
         <v>63</v>
@@ -10863,10 +10860,10 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>36</v>
@@ -10881,13 +10878,13 @@
         <v>168</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H65" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J65" s="5">
         <v>64</v>
@@ -10895,10 +10892,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>36</v>
@@ -10913,13 +10910,13 @@
         <v>104</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H66" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J66" s="5">
         <v>65</v>
@@ -10927,10 +10924,10 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C67" s="13" t="s">
         <v>36</v>
@@ -10945,13 +10942,13 @@
         <v>717</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J67" s="13">
         <v>66</v>
@@ -10959,10 +10956,10 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>36</v>
@@ -10977,13 +10974,13 @@
         <v>212</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H68" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J68" s="6">
         <v>67</v>
@@ -10991,10 +10988,10 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>36</v>
@@ -11009,13 +11006,13 @@
         <v>114</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H69" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J69" s="6">
         <v>68</v>
@@ -11023,10 +11020,10 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>36</v>
@@ -11041,13 +11038,13 @@
         <v>212</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J70" s="6">
         <v>69</v>
@@ -11055,10 +11052,10 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>36</v>
@@ -11073,13 +11070,13 @@
         <v>146</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H71" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J71" s="6">
         <v>70</v>
@@ -11087,10 +11084,10 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>36</v>
@@ -11105,13 +11102,13 @@
         <v>212</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H72" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J72" s="6">
         <v>71</v>
@@ -11119,10 +11116,10 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>36</v>
@@ -11137,13 +11134,13 @@
         <v>183</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J73" s="7">
         <v>72</v>
@@ -11151,10 +11148,10 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>10</v>
@@ -11169,13 +11166,13 @@
         <v>174</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H74" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J74" s="3">
         <v>73</v>
@@ -11183,10 +11180,10 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>10</v>
@@ -11201,13 +11198,13 @@
         <v>81</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H75" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J75" s="3">
         <v>74</v>
@@ -11215,10 +11212,10 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>10</v>
@@ -11233,13 +11230,13 @@
         <v>174</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H76" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J76" s="3">
         <v>75</v>
@@ -11247,10 +11244,10 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>10</v>
@@ -11265,13 +11262,13 @@
         <v>361</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H77" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J77" s="3">
         <v>76</v>
@@ -11279,10 +11276,10 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>10</v>
@@ -11297,13 +11294,13 @@
         <v>174</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H78" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J78" s="3">
         <v>77</v>
@@ -11311,10 +11308,10 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C79" s="11" t="s">
         <v>10</v>
@@ -11329,13 +11326,13 @@
         <v>650</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H79" s="14" t="s">
         <v>20</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J79" s="11">
         <v>78</v>
@@ -11343,10 +11340,10 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>125</v>
+        <v>232</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>10</v>
@@ -11358,16 +11355,16 @@
         <v>12</v>
       </c>
       <c r="F80" s="4">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="H80" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J80" s="4">
         <v>79</v>
@@ -11375,10 +11372,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>125</v>
+        <v>232</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>10</v>
@@ -11390,16 +11387,16 @@
         <v>12</v>
       </c>
       <c r="F81" s="4">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>129</v>
+        <v>237</v>
       </c>
       <c r="H81" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J81" s="4">
         <v>80</v>
@@ -11407,10 +11404,10 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>126</v>
+        <v>231</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>10</v>
@@ -11422,16 +11419,16 @@
         <v>13</v>
       </c>
       <c r="F82" s="4">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>130</v>
+        <v>235</v>
       </c>
       <c r="H82" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J82" s="4">
         <v>81</v>
@@ -11439,10 +11436,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>126</v>
+        <v>231</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>10</v>
@@ -11454,16 +11451,16 @@
         <v>13</v>
       </c>
       <c r="F83" s="4">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>131</v>
+        <v>236</v>
       </c>
       <c r="H83" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J83" s="4">
         <v>82</v>
@@ -11471,10 +11468,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>127</v>
+        <v>230</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>10</v>
@@ -11486,16 +11483,16 @@
         <v>14</v>
       </c>
       <c r="F84" s="4">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>133</v>
+        <v>234</v>
       </c>
       <c r="H84" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J84" s="4">
         <v>83</v>
@@ -11503,10 +11500,10 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
-        <v>127</v>
+        <v>230</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C85" s="12" t="s">
         <v>10</v>
@@ -11518,16 +11515,16 @@
         <v>14</v>
       </c>
       <c r="F85" s="12">
-        <v>186</v>
+        <v>351</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J85" s="12">
         <v>84</v>
@@ -11535,10 +11532,10 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>36</v>
@@ -11553,13 +11550,13 @@
         <v>31</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J86" s="5">
         <v>85</v>
@@ -11567,10 +11564,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>36</v>
@@ -11585,13 +11582,13 @@
         <v>240</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="H87" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J87" s="5">
         <v>86</v>
@@ -11599,10 +11596,10 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>36</v>
@@ -11617,13 +11614,13 @@
         <v>31</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H88" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J88" s="5">
         <v>87</v>
@@ -11631,10 +11628,10 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>36</v>
@@ -11649,13 +11646,13 @@
         <v>824</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="H89" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J89" s="5">
         <v>88</v>
@@ -11663,10 +11660,10 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>36</v>
@@ -11681,13 +11678,13 @@
         <v>31</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="H90" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J90" s="5">
         <v>89</v>
@@ -11695,10 +11692,10 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="13" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C91" s="13" t="s">
         <v>36</v>
@@ -11713,13 +11710,13 @@
         <v>119</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="H91" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J91" s="13">
         <v>90</v>
@@ -11727,10 +11724,10 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="6" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>36</v>
@@ -11745,13 +11742,13 @@
         <v>777</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="H92" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J92" s="6">
         <v>91</v>
@@ -11759,10 +11756,10 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="6" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>36</v>
@@ -11777,13 +11774,13 @@
         <v>3</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="H93" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J93" s="6">
         <v>92</v>
@@ -11791,10 +11788,10 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="6" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>36</v>
@@ -11809,13 +11806,13 @@
         <v>777</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="H94" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J94" s="6">
         <v>93</v>
@@ -11823,10 +11820,10 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>36</v>
@@ -11841,13 +11838,13 @@
         <v>274</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="H95" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J95" s="6">
         <v>94</v>
@@ -11855,10 +11852,10 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="6" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>36</v>
@@ -11873,13 +11870,13 @@
         <v>777</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="H96" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J96" s="6">
         <v>95</v>
@@ -11887,10 +11884,10 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="7" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C97" s="7" t="s">
         <v>36</v>
@@ -11905,13 +11902,13 @@
         <v>83</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="H97" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J97" s="7">
         <v>96</v>
@@ -11919,10 +11916,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>10</v>
@@ -11937,13 +11934,13 @@
         <v>813</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="H98" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J98" s="3">
         <v>97</v>
@@ -11951,10 +11948,10 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>10</v>
@@ -11969,13 +11966,13 @@
         <v>802</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="H99" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J99" s="3">
         <v>98</v>
@@ -11983,10 +11980,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>10</v>
@@ -12001,13 +11998,13 @@
         <v>813</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="H100" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J100" s="3">
         <v>99</v>
@@ -12015,10 +12012,10 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>10</v>
@@ -12033,13 +12030,13 @@
         <v>879</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="H101" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J101" s="3">
         <v>100</v>
@@ -12047,10 +12044,10 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>10</v>
@@ -12065,13 +12062,13 @@
         <v>813</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="H102" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J102" s="3">
         <v>101</v>
@@ -12079,10 +12076,10 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="11" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>10</v>
@@ -12097,13 +12094,13 @@
         <v>281</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="H103" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J103" s="11">
         <v>102</v>
@@ -12111,10 +12108,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>10</v>
@@ -12129,13 +12126,13 @@
         <v>515</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="H104" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J104" s="4">
         <v>103</v>
@@ -12143,10 +12140,10 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>10</v>
@@ -12161,13 +12158,13 @@
         <v>603</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H105" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J105" s="4">
         <v>104</v>
@@ -12175,10 +12172,10 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>10</v>
@@ -12193,13 +12190,13 @@
         <v>515</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J106" s="4">
         <v>105</v>
@@ -12207,10 +12204,10 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>10</v>
@@ -12225,13 +12222,13 @@
         <v>778</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="H107" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J107" s="4">
         <v>106</v>
@@ -12239,10 +12236,10 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>10</v>
@@ -12257,13 +12254,13 @@
         <v>515</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="H108" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J108" s="4">
         <v>107</v>
@@ -12271,10 +12268,10 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="12" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>10</v>
@@ -12289,13 +12286,13 @@
         <v>239</v>
       </c>
       <c r="G109" s="12" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="H109" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="12" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J109" s="12">
         <v>108</v>
@@ -12303,10 +12300,10 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>36</v>
@@ -12321,13 +12318,13 @@
         <v>369</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="H110" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J110" s="5">
         <v>109</v>
@@ -12335,10 +12332,10 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>36</v>
@@ -12353,13 +12350,13 @@
         <v>374</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="H111" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J111" s="5">
         <v>110</v>
@@ -12367,10 +12364,10 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>36</v>
@@ -12385,13 +12382,13 @@
         <v>369</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="H112" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J112" s="5">
         <v>111</v>
@@ -12399,10 +12396,10 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>36</v>
@@ -12417,13 +12414,13 @@
         <v>362</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="H113" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J113" s="5">
         <v>112</v>
@@ -12431,10 +12428,10 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>36</v>
@@ -12449,13 +12446,13 @@
         <v>369</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="H114" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J114" s="5">
         <v>113</v>
@@ -12463,10 +12460,10 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="13" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C115" s="13" t="s">
         <v>36</v>
@@ -12481,13 +12478,13 @@
         <v>793</v>
       </c>
       <c r="G115" s="13" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="H115" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J115" s="13">
         <v>114</v>
@@ -12495,10 +12492,10 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="6" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>36</v>
@@ -12513,13 +12510,13 @@
         <v>371</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="H116" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J116" s="6">
         <v>115</v>
@@ -12527,10 +12524,10 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="6" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>36</v>
@@ -12545,13 +12542,13 @@
         <v>330</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="H117" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J117" s="6">
         <v>116</v>
@@ -12559,10 +12556,10 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="6" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>36</v>
@@ -12577,13 +12574,13 @@
         <v>371</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="H118" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J118" s="6">
         <v>117</v>
@@ -12591,10 +12588,10 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="6" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>36</v>
@@ -12609,13 +12606,13 @@
         <v>759</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="H119" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J119" s="6">
         <v>118</v>
@@ -12623,10 +12620,10 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="6" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>36</v>
@@ -12641,13 +12638,13 @@
         <v>371</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="H120" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="J120" s="6">
         <v>119</v>
@@ -12655,10 +12652,10 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="7" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>36</v>
@@ -12673,13 +12670,13 @@
         <v>729</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="H121" s="10" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="J121" s="7">
         <v>120</v>
@@ -12687,7 +12684,7 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="28" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B125" s="28"/>
     </row>
@@ -12697,7 +12694,7 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="17" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
@@ -12705,7 +12702,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" s="16" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="B130" s="1">
         <f>COUNTIF(H2:H121, "True")</f>
@@ -12714,7 +12711,7 @@
     </row>
     <row r="131" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A131" s="15" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="B131" s="1">
         <f>COUNTIF(H2:H121, "False")</f>
@@ -12723,12 +12720,12 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" s="18" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B144" s="1">
         <f>COUNTIFS(E2:E121, "Low", H2:H121, "True")</f>
@@ -12737,7 +12734,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="B145" s="1">
         <f>COUNTIFS(E2:E121, "Low", H2:H121, "False")</f>
@@ -12746,7 +12743,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B146" s="1">
         <f>COUNTIFS(E2:E121, "Mid", H2:H121, "True")</f>
@@ -12755,7 +12752,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="B147" s="1">
         <f>COUNTIFS(E2:E121, "Mid", H2:H121, "False")</f>
@@ -12764,7 +12761,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="B148" s="1">
         <f>COUNTIFS(E2:E121, "Hig", H2:H121, "True")</f>
@@ -12773,7 +12770,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="B149" s="1">
         <f>COUNTIFS(E2:E121, "Hig", H2:H121, "False")</f>
@@ -12782,12 +12779,12 @@
     </row>
     <row r="156" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A156" s="20" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A158" s="22" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B158" s="21">
         <f>COUNTIFS( I2:I121, "D")</f>
@@ -12796,15 +12793,15 @@
     </row>
     <row r="160" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A160" s="19" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A161" s="19" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B161" s="1">
         <f>COUNTIFS(E2:E121, "Low", H2:H121, "True", I2:I121, "D")</f>
@@ -12813,7 +12810,7 @@
     </row>
     <row r="162" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A162" s="19" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B162" s="1">
         <f>COUNTIFS(E2:E121, "Mid", H2:H121, "True", I2:I121, "D")</f>
@@ -12822,7 +12819,7 @@
     </row>
     <row r="163" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A163" s="19" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B163" s="1">
         <f>COUNTIFS(E2:E121, "Hig", H2:H121, "True", I2:I121, "D")</f>
@@ -12837,12 +12834,12 @@
     </row>
     <row r="169" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="G169" s="19" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="G170" s="1" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="H170" s="1">
         <f>COUNTIFS(I2:I121, "S", H2:H121, "True")</f>
@@ -12851,7 +12848,7 @@
     </row>
     <row r="171" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="G171" s="19" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="H171" s="1">
         <f>COUNTIFS(I2:I121, "D", H2:H121, "True")</f>
@@ -12860,7 +12857,7 @@
     </row>
     <row r="174" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A174" s="22" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="B174" s="21">
         <f>COUNTIFS( I2:I121, "S")</f>
@@ -12869,15 +12866,15 @@
     </row>
     <row r="176" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A176" s="19" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A177" s="19" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B177" s="1">
         <f>COUNTIFS(E2:E121, "Low", H2:H121, "True", I2:I121, "S")</f>
@@ -12886,7 +12883,7 @@
     </row>
     <row r="178" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A178" s="19" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B178" s="1">
         <f>COUNTIFS(E2:E121, "Mid", H2:H121, "True", I2:I121, "S")</f>
@@ -12895,7 +12892,7 @@
     </row>
     <row r="179" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A179" s="19" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B179" s="1">
         <f>COUNTIFS(E2:E121, "Hig", H2:H121, "True", I2:I121, "S")</f>
@@ -12910,12 +12907,12 @@
     </row>
     <row r="191" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A191" s="20" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="21" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="B194" s="21">
         <f>COUNTIFS( B2:B121, "Asian", I2:I121, "D")</f>
@@ -12924,15 +12921,15 @@
     </row>
     <row r="197" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A197" s="19" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A198" s="19" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B198" s="1">
         <f>COUNTIFS( B2:B121, "Asian", I2:I121, "D", H2:H121, "True", E2:E121, "Low")</f>
@@ -12941,7 +12938,7 @@
     </row>
     <row r="199" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A199" s="19" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B199" s="1">
         <f>COUNTIFS( B2:B121, "Asian", I2:I121, "D", H2:H121, "True", E2:E121, "Mid")</f>
@@ -12950,7 +12947,7 @@
     </row>
     <row r="200" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A200" s="19" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B200" s="1">
         <f>COUNTIFS( B2:B121, "Asian", I2:I121, "D", H2:H121, "True", E2:E121, "Hig")</f>
@@ -12959,7 +12956,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="21" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="B203" s="21">
         <f>COUNTIFS( B2:B121, "Black", I2:I121, "D")</f>
@@ -12968,28 +12965,28 @@
     </row>
     <row r="206" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A206" s="19" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="207" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A207" s="19" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B207" s="1">
         <f>COUNTIFS( B2:B121, "Black", I2:I121, "D", H2:H121, "True", E2:E121, "Low")</f>
         <v>4</v>
       </c>
       <c r="D207" s="21" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="E207" s="21"/>
     </row>
     <row r="208" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A208" s="19" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B208" s="1">
         <f>COUNTIFS( B2:B121, "Black", I2:I121, "D", H2:H121, "True", E2:E121, "Mid")</f>
@@ -13004,7 +13001,7 @@
     </row>
     <row r="209" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A209" s="19" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B209" s="1">
         <f>COUNTIFS( B2:B121, "Black", I2:I121, "D", H2:H121, "True", E2:E121, "Hig")</f>
@@ -13027,13 +13024,13 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D211" s="24" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="E211" s="24"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="21" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="B212" s="21">
         <f>COUNTIFS( B2:B121, "Indian", I2:I121, "D")</f>
@@ -13064,19 +13061,19 @@
     </row>
     <row r="215" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A215" s="19" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D215" s="23" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="E215" s="23"/>
     </row>
     <row r="216" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A216" s="19" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B216" s="1">
         <f>COUNTIFS( B2:B121, "Indian", I2:I121, "D", H2:H121, "True", E2:E121, "Low")</f>
@@ -13091,7 +13088,7 @@
     </row>
     <row r="217" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A217" s="19" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B217" s="1">
         <f>COUNTIFS( B2:B121, "Indian", I2:I121, "D", H2:H121, "True", E2:E121, "Mid")</f>
@@ -13106,7 +13103,7 @@
     </row>
     <row r="218" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A218" s="19" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B218" s="1">
         <f>COUNTIFS( B2:B121, "Indian", I2:I121, "D", H2:H121, "True", E2:E121, "Hig")</f>
@@ -13121,7 +13118,7 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D219" s="25" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="E219" s="25"/>
     </row>
@@ -13135,7 +13132,7 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" s="21" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B221" s="21">
         <f>COUNTIFS( B2:B121, "Latino", I2:I121, "D")</f>
@@ -13158,19 +13155,19 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D223" s="26" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="E223" s="26"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B224" s="1">
         <f>COUNTIFS( B2:B121, "Latino", I2:I121, "D", H2:H121, "True", E2:E121, "Low")</f>
@@ -13185,7 +13182,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B225" s="1">
         <f>COUNTIFS( B2:B121, "Latino", I2:I121, "D", H2:H121, "True", E2:E121, "Mid")</f>
@@ -13200,7 +13197,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B226" s="1">
         <f>COUNTIFS( B2:B121, "Latino", I2:I121, "D", H2:H121, "True", E2:E121, "Hig")</f>
@@ -13215,7 +13212,7 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="21" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B229" s="21">
         <f>COUNTIFS( B2:B121, "White", I2:I121, "D")</f>
@@ -13224,15 +13221,15 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="B232" s="1">
         <f>COUNTIFS( B2:B121, "White", I2:I121, "D", H2:H121, "True", E2:E121, "Low")</f>
@@ -13241,7 +13238,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B233" s="1">
         <f>COUNTIFS( B2:B121, "White", I2:I121, "D", H2:H121, "True", E2:E121, "Mid")</f>
@@ -13250,7 +13247,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B234" s="1">
         <f>COUNTIFS( B2:B121, "White", I2:I121, "D", H2:H121, "True", E2:E121, "Hig")</f>
@@ -13263,15 +13260,15 @@
     </row>
     <row r="240" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A240" s="20" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
@@ -13285,7 +13282,7 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="B244" s="1">
         <f>COUNTIFS(C2:C121, "Woman", H2:H121, "True", I2:I121, "D")</f>
@@ -13294,15 +13291,15 @@
     </row>
     <row r="261" spans="1:2" ht="34" x14ac:dyDescent="0.2">
       <c r="A261" s="20" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
